--- a/TREINAMENTO_ FORCAS_QUIPES_BD.xlsx
+++ b/TREINAMENTO_ FORCAS_QUIPES_BD.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupocanel-my.sharepoint.com/personal/elyomidson_brandao_canel_com_br/Documents/Documentos/python-projetos/TREINAMENTO FORCA EQUIPE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ELYOMIDSON.BRANDAO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{42DFF308-9D75-4B7E-A2F4-C3F5F45BE302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{362E4996-66EC-45A4-9DC8-AA2B7E429F97}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A7EA92-BE58-4883-8A66-2521A9F2C00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2C811CF7-C894-4D80-8AC2-C4C3C914DEBA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="217">
   <si>
     <t>TI</t>
   </si>
@@ -497,67 +497,196 @@
     <t>Contabilidade</t>
   </si>
   <si>
-    <t>Adminitrativo</t>
-  </si>
-  <si>
-    <t>Supervisão</t>
-  </si>
-  <si>
     <t>Tecnico de Seguranca</t>
   </si>
   <si>
-    <t>Ajudante de Reflorestamento</t>
-  </si>
-  <si>
     <t>Eucalipto</t>
   </si>
   <si>
-    <t>Almoxarife II</t>
-  </si>
-  <si>
-    <t>Analista Adm Pleno</t>
-  </si>
-  <si>
-    <t>Assistente Administrativo</t>
-  </si>
-  <si>
-    <t>Auxiliar Administrativo</t>
-  </si>
-  <si>
-    <t>Lider de Pecuaria</t>
-  </si>
-  <si>
     <t>Pecuaria</t>
   </si>
   <si>
-    <t>Validar Cargo</t>
-  </si>
-  <si>
     <t>Validar Setor</t>
   </si>
   <si>
-    <t>Auxiliar de Gestao de Servico</t>
-  </si>
-  <si>
-    <t>Lider de Operacoes Agricola</t>
-  </si>
-  <si>
-    <t>Assistente de Granja</t>
-  </si>
-  <si>
-    <t>Assistente de Controle e Qualidade</t>
-  </si>
-  <si>
-    <t>Lider de Manutencao Mecanica</t>
-  </si>
-  <si>
-    <t>Assistente Comercial</t>
-  </si>
-  <si>
-    <t>Analista Adm Senior</t>
-  </si>
-  <si>
-    <t>Assistente Fiscal</t>
+    <t>Gestor</t>
+  </si>
+  <si>
+    <t>Lydyane</t>
+  </si>
+  <si>
+    <t>Fernanda</t>
+  </si>
+  <si>
+    <t>Almoxarifado</t>
+  </si>
+  <si>
+    <t>Elyomidson</t>
+  </si>
+  <si>
+    <t>Jauro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raimundo </t>
+  </si>
+  <si>
+    <t>Alexandre</t>
+  </si>
+  <si>
+    <t>Aplicação</t>
+  </si>
+  <si>
+    <t>Willams</t>
+  </si>
+  <si>
+    <t>Administrativo Canel</t>
+  </si>
+  <si>
+    <t>Isaque</t>
+  </si>
+  <si>
+    <t>João Benvindo</t>
+  </si>
+  <si>
+    <t>Luciano</t>
+  </si>
+  <si>
+    <t>Manutenção Graúna</t>
+  </si>
+  <si>
+    <t>Manutenção Canel</t>
+  </si>
+  <si>
+    <t>Lucas</t>
+  </si>
+  <si>
+    <t>Rubem</t>
+  </si>
+  <si>
+    <t>Produção</t>
+  </si>
+  <si>
+    <t>Francisco</t>
+  </si>
+  <si>
+    <t>Refeitório</t>
+  </si>
+  <si>
+    <t>Chefe de Cozinha</t>
+  </si>
+  <si>
+    <t>Andreia</t>
+  </si>
+  <si>
+    <t>Josípio</t>
+  </si>
+  <si>
+    <t>André</t>
+  </si>
+  <si>
+    <t>Supervisor Administrativo</t>
+  </si>
+  <si>
+    <t>Técnico de Segurança</t>
+  </si>
+  <si>
+    <t>Líder</t>
+  </si>
+  <si>
+    <t>Analista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assistente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auxiliar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Líder </t>
+  </si>
+  <si>
+    <t>Auxiliar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analista </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Almoxarife </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assitente </t>
+  </si>
+  <si>
+    <t>Mélkia</t>
+  </si>
+  <si>
+    <t>Vendedor</t>
+  </si>
+  <si>
+    <t>Caio</t>
+  </si>
+  <si>
+    <t>Portaria</t>
+  </si>
+  <si>
+    <t>Agente de Portaria</t>
+  </si>
+  <si>
+    <t>João Batista</t>
+  </si>
+  <si>
+    <t>Administrativo Lavoro</t>
+  </si>
+  <si>
+    <t>Laelson</t>
+  </si>
+  <si>
+    <t>Pecuária</t>
+  </si>
+  <si>
+    <t>Trabalhador da Pecuária Polivalente</t>
+  </si>
+  <si>
+    <t>Daiza</t>
+  </si>
+  <si>
+    <t>Comprador</t>
+  </si>
+  <si>
+    <t>Usina</t>
+  </si>
+  <si>
+    <t>Operaodor de Moinho</t>
+  </si>
+  <si>
+    <t>Mecânico Industrial</t>
+  </si>
+  <si>
+    <t>Complexo Industrial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador de Pivô </t>
+  </si>
+  <si>
+    <t>Adminitrativo Escritório</t>
+  </si>
+  <si>
+    <t>Recepcionista</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Escritório Teresina</t>
+  </si>
+  <si>
+    <t>Diretoria</t>
+  </si>
+  <si>
+    <t>DGP</t>
+  </si>
+  <si>
+    <t>Almoxarifado Graúna</t>
   </si>
 </sst>
 </file>
@@ -955,23 +1084,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA46323A-AC17-4915-8B32-290002EF3BA9}">
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.21875" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" customWidth="1"/>
-    <col min="4" max="4" width="26.33203125" customWidth="1"/>
-    <col min="5" max="5" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" customWidth="1"/>
-    <col min="7" max="7" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" customWidth="1"/>
-    <col min="9" max="10" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" customWidth="1"/>
-    <col min="12" max="13" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.88671875" customWidth="1"/>
+    <col min="10" max="11" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.33203125" customWidth="1"/>
+    <col min="13" max="14" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>137</v>
       </c>
@@ -982,40 +1112,43 @@
         <v>143</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>138</v>
       </c>
@@ -1026,40 +1159,43 @@
         <v>147</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" t="s">
         <v>127</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>100</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>107</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>116</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>101</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>130</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>117</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>104</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>118</v>
       </c>
-      <c r="N2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>138</v>
       </c>
@@ -1067,43 +1203,46 @@
         <v>93</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>165</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F3" t="s">
         <v>120</v>
       </c>
-      <c r="F3" t="s">
-        <v>115</v>
-      </c>
       <c r="G3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" t="s">
         <v>107</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>116</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>102</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>130</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>108</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>103</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>131</v>
       </c>
-      <c r="N3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>138</v>
       </c>
@@ -1111,43 +1250,46 @@
         <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F4" t="s">
         <v>102</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>121</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>107</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>100</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>101</v>
       </c>
-      <c r="J4" t="s">
-        <v>119</v>
-      </c>
       <c r="K4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L4" t="s">
         <v>103</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>126</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>127</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>138</v>
       </c>
@@ -1155,43 +1297,46 @@
         <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F5" t="s">
         <v>121</v>
       </c>
-      <c r="F5" t="s">
-        <v>115</v>
-      </c>
       <c r="G5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H5" t="s">
         <v>101</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>107</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>131</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>103</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>118</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>126</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>109</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>138</v>
       </c>
@@ -1202,40 +1347,43 @@
         <v>148</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" t="s">
         <v>116</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>120</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>125</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>107</v>
       </c>
-      <c r="I6" t="s">
-        <v>115</v>
-      </c>
       <c r="J6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K6" t="s">
         <v>123</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>118</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>122</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>117</v>
       </c>
-      <c r="N6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>138</v>
       </c>
@@ -1246,40 +1394,43 @@
         <v>149</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F7" t="s">
         <v>107</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>125</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>108</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>128</v>
       </c>
-      <c r="I7" t="s">
-        <v>119</v>
-      </c>
       <c r="J7" t="s">
+        <v>119</v>
+      </c>
+      <c r="K7" t="s">
         <v>117</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>109</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>131</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>123</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>138</v>
       </c>
@@ -1290,40 +1441,43 @@
         <v>150</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F8" t="s">
         <v>126</v>
       </c>
-      <c r="F8" t="s">
-        <v>115</v>
-      </c>
       <c r="G8" t="s">
+        <v>115</v>
+      </c>
+      <c r="H8" t="s">
         <v>107</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>100</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>125</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>106</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>109</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>117</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>123</v>
       </c>
-      <c r="N8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>138</v>
       </c>
@@ -1331,43 +1485,46 @@
         <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F9" t="s">
         <v>120</v>
       </c>
-      <c r="F9" t="s">
-        <v>115</v>
-      </c>
       <c r="G9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H9" t="s">
         <v>122</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>121</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>105</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>101</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>109</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>131</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>102</v>
       </c>
-      <c r="N9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>138</v>
       </c>
@@ -1375,43 +1532,46 @@
         <v>32</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E10" t="s">
+        <v>164</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F10" t="s">
         <v>100</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>107</v>
       </c>
-      <c r="G10" t="s">
-        <v>119</v>
-      </c>
       <c r="H10" t="s">
+        <v>119</v>
+      </c>
+      <c r="I10" t="s">
         <v>130</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>108</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>122</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>106</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>109</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>118</v>
       </c>
-      <c r="N10" t="s">
+      <c r="O10" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>138</v>
       </c>
@@ -1422,40 +1582,43 @@
         <v>165</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E11" t="s">
-        <v>115</v>
+        <v>166</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="F11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G11" t="s">
         <v>100</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>129</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>122</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>105</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>130</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>117</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>123</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>131</v>
       </c>
-      <c r="N11" t="s">
+      <c r="O11" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>138</v>
       </c>
@@ -1463,43 +1626,46 @@
         <v>62</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E12" t="s">
-        <v>119</v>
+        <v>168</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>189</v>
       </c>
       <c r="F12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" t="s">
         <v>127</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>103</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>109</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>106</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>107</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>125</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>131</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>128</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>138</v>
       </c>
@@ -1507,43 +1673,46 @@
         <v>46</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F13" t="s">
         <v>123</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>107</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>100</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>121</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>101</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>118</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>117</v>
       </c>
-      <c r="L13" t="s">
-        <v>119</v>
-      </c>
       <c r="M13" t="s">
+        <v>119</v>
+      </c>
+      <c r="N13" t="s">
         <v>127</v>
       </c>
-      <c r="N13" t="s">
+      <c r="O13" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>138</v>
       </c>
@@ -1554,40 +1723,43 @@
         <v>7</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E14" t="s">
-        <v>115</v>
+        <v>10</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="F14" t="s">
+        <v>115</v>
+      </c>
+      <c r="G14" t="s">
         <v>107</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>116</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>129</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>106</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>105</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>102</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>118</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>126</v>
       </c>
-      <c r="N14" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>138</v>
       </c>
@@ -1598,40 +1770,43 @@
         <v>5</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E15" t="s">
+        <v>170</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F15" t="s">
         <v>120</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>106</v>
       </c>
-      <c r="G15" t="s">
-        <v>115</v>
-      </c>
       <c r="H15" t="s">
+        <v>115</v>
+      </c>
+      <c r="I15" t="s">
         <v>116</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>125</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>118</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>102</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>131</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>126</v>
       </c>
-      <c r="N15" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>138</v>
       </c>
@@ -1639,43 +1814,46 @@
         <v>92</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E16" t="s">
+        <v>171</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F16" t="s">
         <v>125</v>
       </c>
-      <c r="F16" t="s">
-        <v>115</v>
-      </c>
       <c r="G16" t="s">
+        <v>115</v>
+      </c>
+      <c r="H16" t="s">
         <v>116</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>101</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>100</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>123</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>102</v>
       </c>
-      <c r="L16" t="s">
-        <v>119</v>
-      </c>
       <c r="M16" t="s">
+        <v>119</v>
+      </c>
+      <c r="N16" t="s">
         <v>131</v>
       </c>
-      <c r="N16" t="s">
+      <c r="O16" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>138</v>
       </c>
@@ -1683,43 +1861,46 @@
         <v>57</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>165</v>
+        <v>4</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E17" t="s">
-        <v>115</v>
+        <v>174</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="F17" t="s">
+        <v>115</v>
+      </c>
+      <c r="G17" t="s">
         <v>100</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>121</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>109</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>124</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>108</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" t="s">
         <v>118</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>131</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>123</v>
       </c>
-      <c r="N17" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>138</v>
       </c>
@@ -1730,40 +1911,43 @@
         <v>145</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F18" t="s">
         <v>106</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>116</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>129</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>101</v>
       </c>
-      <c r="I18" t="s">
-        <v>115</v>
-      </c>
       <c r="J18" t="s">
+        <v>115</v>
+      </c>
+      <c r="K18" t="s">
         <v>130</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>107</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
         <v>100</v>
       </c>
-      <c r="M18" t="s">
-        <v>119</v>
-      </c>
       <c r="N18" t="s">
+        <v>119</v>
+      </c>
+      <c r="O18" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>139</v>
       </c>
@@ -1774,40 +1958,43 @@
         <v>146</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E19" t="s">
+        <v>168</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F19" t="s">
         <v>127</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>106</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>125</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>104</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>116</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>105</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>128</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>118</v>
       </c>
-      <c r="M19" t="s">
-        <v>119</v>
-      </c>
       <c r="N19" t="s">
+        <v>119</v>
+      </c>
+      <c r="O19" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>139</v>
       </c>
@@ -1818,40 +2005,43 @@
         <v>3</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E20" t="s">
-        <v>115</v>
+        <v>86</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="F20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G20" t="s">
         <v>107</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>121</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>108</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>118</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>103</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
         <v>117</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>122</v>
       </c>
-      <c r="M20" t="s">
-        <v>119</v>
-      </c>
       <c r="N20" t="s">
+        <v>119</v>
+      </c>
+      <c r="O20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>139</v>
       </c>
@@ -1859,43 +2049,46 @@
         <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E21" t="s">
-        <v>115</v>
+        <v>159</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="F21" t="s">
+        <v>115</v>
+      </c>
+      <c r="G21" t="s">
         <v>100</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>121</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>101</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>122</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>126</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>103</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>120</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>116</v>
       </c>
-      <c r="N21" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>139</v>
       </c>
@@ -1903,43 +2096,46 @@
         <v>79</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E22" t="s">
-        <v>115</v>
+        <v>176</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="F22" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" t="s">
         <v>107</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>116</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>102</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>120</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>118</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>124</v>
       </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>122</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>105</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>139</v>
       </c>
@@ -1947,43 +2143,46 @@
         <v>64</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E23" t="s">
+        <v>168</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F23" t="s">
         <v>106</v>
       </c>
-      <c r="F23" t="s">
-        <v>115</v>
-      </c>
       <c r="G23" t="s">
+        <v>115</v>
+      </c>
+      <c r="H23" t="s">
         <v>105</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>120</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>125</v>
       </c>
-      <c r="J23" t="s">
-        <v>119</v>
-      </c>
       <c r="K23" t="s">
+        <v>119</v>
+      </c>
+      <c r="L23" t="s">
         <v>117</v>
       </c>
-      <c r="L23" t="s">
+      <c r="M23" t="s">
         <v>123</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>118</v>
       </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>139</v>
       </c>
@@ -1994,40 +2193,43 @@
         <v>165</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E24" t="s">
-        <v>115</v>
+        <v>166</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="F24" t="s">
+        <v>115</v>
+      </c>
+      <c r="G24" t="s">
         <v>116</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>120</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>106</v>
       </c>
-      <c r="I24" t="s">
-        <v>119</v>
-      </c>
       <c r="J24" t="s">
+        <v>119</v>
+      </c>
+      <c r="K24" t="s">
         <v>103</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>117</v>
       </c>
-      <c r="L24" t="s">
+      <c r="M24" t="s">
         <v>133</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
         <v>128</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>139</v>
       </c>
@@ -2038,40 +2240,43 @@
         <v>1</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E25" t="s">
+        <v>179</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F25" t="s">
         <v>107</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>120</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>123</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>105</v>
       </c>
-      <c r="I25" t="s">
-        <v>115</v>
-      </c>
       <c r="J25" t="s">
+        <v>115</v>
+      </c>
+      <c r="K25" t="s">
         <v>118</v>
       </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
         <v>122</v>
       </c>
-      <c r="L25" t="s">
-        <v>119</v>
-      </c>
       <c r="M25" t="s">
+        <v>119</v>
+      </c>
+      <c r="N25" t="s">
         <v>128</v>
       </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>139</v>
       </c>
@@ -2079,43 +2284,46 @@
         <v>19</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E26" t="s">
+        <v>159</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F26" t="s">
         <v>102</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>120</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>126</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>123</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>107</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>128</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>118</v>
       </c>
-      <c r="L26" t="s">
+      <c r="M26" t="s">
         <v>134</v>
       </c>
-      <c r="M26" t="s">
-        <v>119</v>
-      </c>
       <c r="N26" t="s">
+        <v>119</v>
+      </c>
+      <c r="O26" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>139</v>
       </c>
@@ -2126,40 +2334,43 @@
         <v>0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E27" t="s">
+        <v>180</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F27" t="s">
         <v>105</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>120</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>134</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>108</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>121</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>124</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
         <v>136</v>
       </c>
-      <c r="L27" t="s">
+      <c r="M27" t="s">
         <v>102</v>
       </c>
-      <c r="M27" t="s">
+      <c r="N27" t="s">
         <v>104</v>
       </c>
-      <c r="N27" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O27" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>139</v>
       </c>
@@ -2170,40 +2381,43 @@
         <v>151</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E28" t="s">
-        <v>115</v>
+        <v>181</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="F28" t="s">
+        <v>115</v>
+      </c>
+      <c r="G28" t="s">
         <v>116</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>117</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>122</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>125</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>127</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
         <v>109</v>
       </c>
-      <c r="L28" t="s">
+      <c r="M28" t="s">
         <v>105</v>
       </c>
-      <c r="M28" t="s">
-        <v>119</v>
-      </c>
       <c r="N28" t="s">
+        <v>119</v>
+      </c>
+      <c r="O28" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>139</v>
       </c>
@@ -2211,43 +2425,46 @@
         <v>9</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>165</v>
+        <v>7</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E29" t="s">
-        <v>115</v>
+        <v>10</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="F29" t="s">
+        <v>115</v>
+      </c>
+      <c r="G29" t="s">
         <v>100</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>124</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>134</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>125</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>128</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
         <v>107</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
         <v>102</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" t="s">
         <v>126</v>
       </c>
-      <c r="N29" t="s">
+      <c r="O29" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>139</v>
       </c>
@@ -2258,40 +2475,43 @@
         <v>147</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E30" t="s">
-        <v>115</v>
+        <v>158</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>183</v>
       </c>
       <c r="F30" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" t="s">
         <v>106</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>128</v>
       </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>134</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>108</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>123</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
         <v>118</v>
       </c>
-      <c r="L30" t="s">
-        <v>119</v>
-      </c>
       <c r="M30" t="s">
+        <v>119</v>
+      </c>
+      <c r="N30" t="s">
         <v>103</v>
       </c>
-      <c r="N30" t="s">
+      <c r="O30" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>139</v>
       </c>
@@ -2302,40 +2522,43 @@
         <v>5</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E31" t="s">
+        <v>170</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F31" t="s">
         <v>127</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>122</v>
       </c>
-      <c r="G31" t="s">
-        <v>115</v>
-      </c>
       <c r="H31" t="s">
+        <v>115</v>
+      </c>
+      <c r="I31" t="s">
         <v>134</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>100</v>
       </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>102</v>
       </c>
-      <c r="K31" t="s">
+      <c r="L31" t="s">
         <v>117</v>
       </c>
-      <c r="L31" t="s">
+      <c r="M31" t="s">
         <v>118</v>
       </c>
-      <c r="M31" t="s">
+      <c r="N31" t="s">
         <v>109</v>
       </c>
-      <c r="N31" t="s">
+      <c r="O31" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>139</v>
       </c>
@@ -2346,40 +2569,43 @@
         <v>2</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E32" t="s">
-        <v>115</v>
+        <v>193</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="F32" t="s">
+        <v>115</v>
+      </c>
+      <c r="G32" t="s">
         <v>120</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>116</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>122</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>100</v>
       </c>
-      <c r="J32" t="s">
-        <v>119</v>
-      </c>
       <c r="K32" t="s">
+        <v>119</v>
+      </c>
+      <c r="L32" t="s">
         <v>118</v>
       </c>
-      <c r="L32" t="s">
+      <c r="M32" t="s">
         <v>117</v>
       </c>
-      <c r="M32" t="s">
+      <c r="N32" t="s">
         <v>102</v>
       </c>
-      <c r="N32" t="s">
+      <c r="O32" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>139</v>
       </c>
@@ -2390,40 +2616,43 @@
         <v>149</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E33" t="s">
+        <v>158</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F33" t="s">
         <v>100</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>101</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>102</v>
       </c>
-      <c r="H33" t="s">
+      <c r="I33" t="s">
         <v>103</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>104</v>
       </c>
-      <c r="J33" t="s">
-        <v>115</v>
-      </c>
       <c r="K33" t="s">
+        <v>115</v>
+      </c>
+      <c r="L33" t="s">
         <v>116</v>
       </c>
-      <c r="L33" t="s">
+      <c r="M33" t="s">
         <v>117</v>
       </c>
-      <c r="M33" t="s">
+      <c r="N33" t="s">
         <v>118</v>
       </c>
-      <c r="N33" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O33" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>139</v>
       </c>
@@ -2431,43 +2660,46 @@
         <v>80</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E34" t="s">
+        <v>176</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F34" t="s">
         <v>120</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>121</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>101</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
         <v>122</v>
       </c>
-      <c r="I34" t="s">
+      <c r="J34" t="s">
         <v>105</v>
       </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>123</v>
       </c>
-      <c r="K34" t="s">
+      <c r="L34" t="s">
         <v>124</v>
       </c>
-      <c r="L34" t="s">
+      <c r="M34" t="s">
         <v>102</v>
       </c>
-      <c r="M34" t="s">
+      <c r="N34" t="s">
         <v>104</v>
       </c>
-      <c r="N34" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O34" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>139</v>
       </c>
@@ -2478,40 +2710,43 @@
         <v>145</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E35" t="s">
+        <v>159</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F35" t="s">
         <v>121</v>
       </c>
-      <c r="F35" t="s">
-        <v>115</v>
-      </c>
       <c r="G35" t="s">
+        <v>115</v>
+      </c>
+      <c r="H35" t="s">
         <v>116</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
         <v>101</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>125</v>
       </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>128</v>
       </c>
-      <c r="K35" t="s">
+      <c r="L35" t="s">
         <v>107</v>
       </c>
-      <c r="L35" t="s">
+      <c r="M35" t="s">
         <v>109</v>
       </c>
-      <c r="M35" t="s">
-        <v>119</v>
-      </c>
       <c r="N35" t="s">
+        <v>119</v>
+      </c>
+      <c r="O35" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>139</v>
       </c>
@@ -2519,43 +2754,46 @@
         <v>58</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>165</v>
+        <v>4</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E36" t="s">
+        <v>174</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F36" t="s">
         <v>100</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>121</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>101</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>116</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
         <v>102</v>
       </c>
-      <c r="J36" t="s">
+      <c r="K36" t="s">
         <v>106</v>
       </c>
-      <c r="K36" t="s">
+      <c r="L36" t="s">
         <v>104</v>
       </c>
-      <c r="L36" t="s">
+      <c r="M36" t="s">
         <v>109</v>
       </c>
-      <c r="M36" t="s">
+      <c r="N36" t="s">
         <v>118</v>
       </c>
-      <c r="N36" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O36" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>140</v>
       </c>
@@ -2566,40 +2804,43 @@
         <v>7</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E37" t="s">
+        <v>181</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F37" t="s">
         <v>121</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>101</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>120</v>
       </c>
-      <c r="H37" t="s">
-        <v>115</v>
-      </c>
       <c r="I37" t="s">
+        <v>115</v>
+      </c>
+      <c r="J37" t="s">
         <v>122</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>108</v>
       </c>
-      <c r="K37" t="s">
+      <c r="L37" t="s">
         <v>117</v>
       </c>
-      <c r="L37" t="s">
+      <c r="M37" t="s">
         <v>106</v>
       </c>
-      <c r="M37" t="s">
+      <c r="N37" t="s">
         <v>126</v>
       </c>
-      <c r="N37" t="s">
+      <c r="O37" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>140</v>
       </c>
@@ -2610,40 +2851,43 @@
         <v>6</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E38" t="s">
+        <v>195</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F38" t="s">
         <v>116</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>102</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>120</v>
       </c>
-      <c r="H38" t="s">
+      <c r="I38" t="s">
         <v>106</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>100</v>
       </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
         <v>117</v>
       </c>
-      <c r="K38" t="s">
+      <c r="L38" t="s">
         <v>123</v>
       </c>
-      <c r="L38" t="s">
+      <c r="M38" t="s">
         <v>103</v>
       </c>
-      <c r="M38" t="s">
+      <c r="N38" t="s">
         <v>107</v>
       </c>
-      <c r="N38" t="s">
+      <c r="O38" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>140</v>
       </c>
@@ -2651,43 +2895,46 @@
         <v>69</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E39" t="s">
+        <v>168</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F39" t="s">
         <v>107</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>100</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>101</v>
       </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
         <v>102</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>103</v>
       </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>130</v>
       </c>
-      <c r="K39" t="s">
+      <c r="L39" t="s">
         <v>109</v>
       </c>
-      <c r="L39" t="s">
+      <c r="M39" t="s">
         <v>106</v>
       </c>
-      <c r="M39" t="s">
-        <v>119</v>
-      </c>
       <c r="N39" t="s">
+        <v>119</v>
+      </c>
+      <c r="O39" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>140</v>
       </c>
@@ -2698,40 +2945,43 @@
         <v>3</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E40" t="s">
+        <v>198</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F40" t="s">
         <v>100</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>107</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>124</v>
       </c>
-      <c r="H40" t="s">
+      <c r="I40" t="s">
         <v>105</v>
       </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>120</v>
       </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>128</v>
       </c>
-      <c r="K40" t="s">
+      <c r="L40" t="s">
         <v>109</v>
       </c>
-      <c r="L40" t="s">
+      <c r="M40" t="s">
         <v>106</v>
       </c>
-      <c r="M40" t="s">
+      <c r="N40" t="s">
         <v>117</v>
       </c>
-      <c r="N40" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O40" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>140</v>
       </c>
@@ -2739,43 +2989,46 @@
         <v>23</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E41" t="s">
+        <v>159</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F41" t="s">
         <v>120</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>126</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>123</v>
       </c>
-      <c r="H41" t="s">
+      <c r="I41" t="s">
         <v>122</v>
       </c>
-      <c r="I41" t="s">
+      <c r="J41" t="s">
         <v>106</v>
       </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>109</v>
       </c>
-      <c r="K41" t="s">
+      <c r="L41" t="s">
         <v>104</v>
       </c>
-      <c r="L41" t="s">
+      <c r="M41" t="s">
         <v>121</v>
       </c>
-      <c r="M41" t="s">
+      <c r="N41" t="s">
         <v>108</v>
       </c>
-      <c r="N41" t="s">
+      <c r="O41" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>140</v>
       </c>
@@ -2783,43 +3036,46 @@
         <v>65</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E42" t="s">
-        <v>115</v>
+        <v>168</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="F42" t="s">
+        <v>115</v>
+      </c>
+      <c r="G42" t="s">
         <v>107</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>126</v>
       </c>
-      <c r="H42" t="s">
+      <c r="I42" t="s">
         <v>121</v>
       </c>
-      <c r="I42" t="s">
+      <c r="J42" t="s">
         <v>100</v>
       </c>
-      <c r="J42" t="s">
+      <c r="K42" t="s">
         <v>120</v>
       </c>
-      <c r="K42" t="s">
+      <c r="L42" t="s">
         <v>125</v>
       </c>
-      <c r="L42" t="s">
+      <c r="M42" t="s">
         <v>104</v>
       </c>
-      <c r="M42" t="s">
-        <v>119</v>
-      </c>
       <c r="N42" t="s">
+        <v>119</v>
+      </c>
+      <c r="O42" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>140</v>
       </c>
@@ -2830,40 +3086,43 @@
         <v>0</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E43" t="s">
+        <v>180</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F43" t="s">
         <v>105</v>
       </c>
-      <c r="F43" t="s">
-        <v>115</v>
-      </c>
       <c r="G43" t="s">
+        <v>115</v>
+      </c>
+      <c r="H43" t="s">
         <v>102</v>
       </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
         <v>127</v>
       </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
         <v>106</v>
       </c>
-      <c r="J43" t="s">
+      <c r="K43" t="s">
         <v>128</v>
       </c>
-      <c r="K43" t="s">
+      <c r="L43" t="s">
         <v>125</v>
       </c>
-      <c r="L43" t="s">
+      <c r="M43" t="s">
         <v>109</v>
       </c>
-      <c r="M43" t="s">
+      <c r="N43" t="s">
         <v>116</v>
       </c>
-      <c r="N43" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O43" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>140</v>
       </c>
@@ -2871,43 +3130,46 @@
         <v>52</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E44" t="s">
+        <v>169</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F44" t="s">
         <v>124</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>107</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>116</v>
       </c>
-      <c r="H44" t="s">
+      <c r="I44" t="s">
         <v>120</v>
       </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>125</v>
       </c>
-      <c r="J44" t="s">
+      <c r="K44" t="s">
         <v>118</v>
       </c>
-      <c r="K44" t="s">
+      <c r="L44" t="s">
         <v>102</v>
       </c>
-      <c r="L44" t="s">
+      <c r="M44" t="s">
         <v>106</v>
       </c>
-      <c r="M44" t="s">
-        <v>119</v>
-      </c>
       <c r="N44" t="s">
+        <v>119</v>
+      </c>
+      <c r="O44" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>140</v>
       </c>
@@ -2915,43 +3177,46 @@
         <v>43</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E45" t="s">
-        <v>115</v>
+        <v>200</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="F45" t="s">
+        <v>115</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>121</v>
       </c>
-      <c r="H45" t="s">
+      <c r="I45" t="s">
         <v>101</v>
       </c>
-      <c r="I45" t="s">
+      <c r="J45" t="s">
         <v>107</v>
       </c>
-      <c r="J45" t="s">
+      <c r="K45" t="s">
         <v>116</v>
       </c>
-      <c r="K45" t="s">
+      <c r="L45" t="s">
         <v>117</v>
       </c>
-      <c r="L45" t="s">
+      <c r="M45" t="s">
         <v>128</v>
       </c>
-      <c r="M45" t="s">
-        <v>119</v>
-      </c>
       <c r="N45" t="s">
+        <v>119</v>
+      </c>
+      <c r="O45" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>140</v>
       </c>
@@ -2959,43 +3224,46 @@
         <v>61</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>165</v>
+        <v>4</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E46" t="s">
+        <v>174</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F46" t="s">
         <v>121</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>127</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>104</v>
       </c>
-      <c r="H46" t="s">
+      <c r="I46" t="s">
         <v>122</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>105</v>
       </c>
-      <c r="J46" t="s">
-        <v>119</v>
-      </c>
       <c r="K46" t="s">
+        <v>119</v>
+      </c>
+      <c r="L46" t="s">
         <v>108</v>
       </c>
-      <c r="L46" t="s">
+      <c r="M46" t="s">
         <v>103</v>
       </c>
-      <c r="M46" t="s">
+      <c r="N46" t="s">
         <v>128</v>
       </c>
-      <c r="N46" t="s">
+      <c r="O46" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>140</v>
       </c>
@@ -3006,40 +3274,43 @@
         <v>1</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E47" t="s">
+        <v>179</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F47" t="s">
         <v>100</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>126</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>120</v>
       </c>
-      <c r="H47" t="s">
+      <c r="I47" t="s">
         <v>105</v>
       </c>
-      <c r="I47" t="s">
+      <c r="J47" t="s">
         <v>127</v>
       </c>
-      <c r="J47" t="s">
+      <c r="K47" t="s">
         <v>125</v>
       </c>
-      <c r="K47" t="s">
+      <c r="L47" t="s">
         <v>102</v>
       </c>
-      <c r="L47" t="s">
+      <c r="M47" t="s">
         <v>128</v>
       </c>
-      <c r="M47" t="s">
+      <c r="N47" t="s">
         <v>106</v>
       </c>
-      <c r="N47" t="s">
+      <c r="O47" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>140</v>
       </c>
@@ -3050,40 +3321,43 @@
         <v>5</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E48" t="s">
+        <v>195</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F48" t="s">
         <v>100</v>
       </c>
-      <c r="F48" t="s">
-        <v>115</v>
-      </c>
       <c r="G48" t="s">
+        <v>115</v>
+      </c>
+      <c r="H48" t="s">
         <v>106</v>
       </c>
-      <c r="H48" t="s">
+      <c r="I48" t="s">
         <v>121</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>126</v>
       </c>
-      <c r="J48" t="s">
+      <c r="K48" t="s">
         <v>123</v>
       </c>
-      <c r="K48" t="s">
+      <c r="L48" t="s">
         <v>128</v>
       </c>
-      <c r="L48" t="s">
+      <c r="M48" t="s">
         <v>117</v>
       </c>
-      <c r="M48" t="s">
-        <v>119</v>
-      </c>
       <c r="N48" t="s">
+        <v>119</v>
+      </c>
+      <c r="O48" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>140</v>
       </c>
@@ -3091,43 +3365,46 @@
         <v>33</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F49" t="s">
         <v>121</v>
       </c>
-      <c r="F49" t="s">
-        <v>115</v>
-      </c>
       <c r="G49" t="s">
+        <v>115</v>
+      </c>
+      <c r="H49" t="s">
         <v>120</v>
       </c>
-      <c r="H49" t="s">
+      <c r="I49" t="s">
         <v>125</v>
       </c>
-      <c r="I49" t="s">
+      <c r="J49" t="s">
         <v>128</v>
       </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
         <v>106</v>
       </c>
-      <c r="K49" t="s">
-        <v>119</v>
-      </c>
       <c r="L49" t="s">
+        <v>119</v>
+      </c>
+      <c r="M49" t="s">
         <v>127</v>
       </c>
-      <c r="M49" t="s">
+      <c r="N49" t="s">
         <v>126</v>
       </c>
-      <c r="N49" t="s">
+      <c r="O49" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>140</v>
       </c>
@@ -3138,40 +3415,43 @@
         <v>3</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E50" t="s">
+        <v>203</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" t="s">
         <v>100</v>
       </c>
-      <c r="F50" t="s">
-        <v>115</v>
-      </c>
       <c r="G50" t="s">
+        <v>115</v>
+      </c>
+      <c r="H50" t="s">
         <v>107</v>
       </c>
-      <c r="H50" t="s">
+      <c r="I50" t="s">
         <v>127</v>
       </c>
-      <c r="I50" t="s">
+      <c r="J50" t="s">
         <v>126</v>
       </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
         <v>102</v>
       </c>
-      <c r="K50" t="s">
+      <c r="L50" t="s">
         <v>104</v>
       </c>
-      <c r="L50" t="s">
-        <v>119</v>
-      </c>
       <c r="M50" t="s">
+        <v>119</v>
+      </c>
+      <c r="N50" t="s">
         <v>109</v>
       </c>
-      <c r="N50" t="s">
+      <c r="O50" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>140</v>
       </c>
@@ -3182,40 +3462,43 @@
         <v>149</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E51" t="s">
+        <v>158</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F51" t="s">
         <v>107</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>116</v>
       </c>
-      <c r="G51" t="s">
-        <v>115</v>
-      </c>
       <c r="H51" t="s">
+        <v>115</v>
+      </c>
+      <c r="I51" t="s">
         <v>100</v>
       </c>
-      <c r="I51" t="s">
+      <c r="J51" t="s">
         <v>101</v>
       </c>
-      <c r="J51" t="s">
+      <c r="K51" t="s">
         <v>127</v>
       </c>
-      <c r="K51" t="s">
+      <c r="L51" t="s">
         <v>106</v>
       </c>
-      <c r="L51" t="s">
+      <c r="M51" t="s">
         <v>117</v>
       </c>
-      <c r="M51" t="s">
-        <v>119</v>
-      </c>
       <c r="N51" t="s">
+        <v>119</v>
+      </c>
+      <c r="O51" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>140</v>
       </c>
@@ -3226,40 +3509,43 @@
         <v>165</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E52" t="s">
+        <v>166</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F52" t="s">
         <v>122</v>
       </c>
-      <c r="F52" t="s">
-        <v>115</v>
-      </c>
       <c r="G52" t="s">
+        <v>115</v>
+      </c>
+      <c r="H52" t="s">
         <v>120</v>
       </c>
-      <c r="H52" t="s">
+      <c r="I52" t="s">
         <v>125</v>
       </c>
-      <c r="I52" t="s">
+      <c r="J52" t="s">
         <v>101</v>
       </c>
-      <c r="J52" t="s">
+      <c r="K52" t="s">
         <v>104</v>
       </c>
-      <c r="K52" t="s">
+      <c r="L52" t="s">
         <v>127</v>
       </c>
-      <c r="L52" t="s">
+      <c r="M52" t="s">
         <v>107</v>
       </c>
-      <c r="M52" t="s">
+      <c r="N52" t="s">
         <v>118</v>
       </c>
-      <c r="N52" t="s">
+      <c r="O52" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>140</v>
       </c>
@@ -3270,40 +3556,43 @@
         <v>145</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E53" t="s">
-        <v>115</v>
+        <v>159</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>204</v>
       </c>
       <c r="F53" t="s">
+        <v>115</v>
+      </c>
+      <c r="G53" t="s">
         <v>121</v>
       </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>120</v>
       </c>
-      <c r="H53" t="s">
+      <c r="I53" t="s">
         <v>122</v>
       </c>
-      <c r="I53" t="s">
+      <c r="J53" t="s">
         <v>101</v>
       </c>
-      <c r="J53" t="s">
+      <c r="K53" t="s">
         <v>107</v>
       </c>
-      <c r="K53" t="s">
+      <c r="L53" t="s">
         <v>106</v>
       </c>
-      <c r="L53" t="s">
+      <c r="M53" t="s">
         <v>103</v>
       </c>
-      <c r="M53" t="s">
+      <c r="N53" t="s">
         <v>104</v>
       </c>
-      <c r="N53" t="s">
+      <c r="O53" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>141</v>
       </c>
@@ -3314,40 +3603,43 @@
         <v>152</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E54" t="s">
+        <v>198</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F54" t="s">
         <v>102</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>126</v>
       </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
         <v>107</v>
       </c>
-      <c r="H54" t="s">
+      <c r="I54" t="s">
         <v>120</v>
       </c>
-      <c r="I54" t="s">
+      <c r="J54" t="s">
         <v>116</v>
       </c>
-      <c r="J54" t="s">
+      <c r="K54" t="s">
         <v>123</v>
       </c>
-      <c r="K54" t="s">
+      <c r="L54" t="s">
         <v>103</v>
       </c>
-      <c r="L54" t="s">
+      <c r="M54" t="s">
         <v>109</v>
       </c>
-      <c r="M54" t="s">
-        <v>119</v>
-      </c>
       <c r="N54" t="s">
+        <v>119</v>
+      </c>
+      <c r="O54" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>141</v>
       </c>
@@ -3358,40 +3650,43 @@
         <v>1</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E55" t="s">
-        <v>115</v>
+        <v>179</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="F55" t="s">
+        <v>115</v>
+      </c>
+      <c r="G55" t="s">
         <v>107</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>120</v>
       </c>
-      <c r="H55" t="s">
+      <c r="I55" t="s">
         <v>125</v>
       </c>
-      <c r="I55" t="s">
+      <c r="J55" t="s">
         <v>101</v>
       </c>
-      <c r="J55" t="s">
+      <c r="K55" t="s">
         <v>103</v>
       </c>
-      <c r="K55" t="s">
+      <c r="L55" t="s">
         <v>109</v>
       </c>
-      <c r="L55" t="s">
+      <c r="M55" t="s">
         <v>135</v>
       </c>
-      <c r="M55" t="s">
+      <c r="N55" t="s">
         <v>102</v>
       </c>
-      <c r="N55" t="s">
+      <c r="O55" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>141</v>
       </c>
@@ -3401,41 +3696,44 @@
       <c r="C56" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="D56" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F56" t="s">
         <v>125</v>
       </c>
-      <c r="F56" t="s">
-        <v>115</v>
-      </c>
       <c r="G56" t="s">
+        <v>115</v>
+      </c>
+      <c r="H56" t="s">
         <v>129</v>
       </c>
-      <c r="H56" t="s">
+      <c r="I56" t="s">
         <v>121</v>
       </c>
-      <c r="I56" t="s">
+      <c r="J56" t="s">
         <v>106</v>
       </c>
-      <c r="J56" t="s">
+      <c r="K56" t="s">
         <v>123</v>
       </c>
-      <c r="K56" t="s">
-        <v>119</v>
-      </c>
       <c r="L56" t="s">
+        <v>119</v>
+      </c>
+      <c r="M56" t="s">
         <v>109</v>
       </c>
-      <c r="M56" t="s">
+      <c r="N56" t="s">
         <v>103</v>
       </c>
-      <c r="N56" t="s">
+      <c r="O56" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>141</v>
       </c>
@@ -3443,43 +3741,46 @@
         <v>91</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E57" t="s">
-        <v>115</v>
+        <v>92</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>189</v>
       </c>
       <c r="F57" t="s">
+        <v>115</v>
+      </c>
+      <c r="G57" t="s">
         <v>121</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>101</v>
       </c>
-      <c r="H57" t="s">
+      <c r="I57" t="s">
         <v>116</v>
       </c>
-      <c r="I57" t="s">
+      <c r="J57" t="s">
         <v>100</v>
       </c>
-      <c r="J57" t="s">
+      <c r="K57" t="s">
         <v>124</v>
       </c>
-      <c r="K57" t="s">
+      <c r="L57" t="s">
         <v>128</v>
       </c>
-      <c r="L57" t="s">
-        <v>119</v>
-      </c>
       <c r="M57" t="s">
+        <v>119</v>
+      </c>
+      <c r="N57" t="s">
         <v>132</v>
       </c>
-      <c r="N57" t="s">
+      <c r="O57" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>141</v>
       </c>
@@ -3487,43 +3788,46 @@
         <v>84</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E58" t="s">
-        <v>115</v>
+        <v>162</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>206</v>
       </c>
       <c r="F58" t="s">
+        <v>115</v>
+      </c>
+      <c r="G58" t="s">
         <v>117</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>122</v>
       </c>
-      <c r="H58" t="s">
+      <c r="I58" t="s">
         <v>107</v>
       </c>
-      <c r="I58" t="s">
+      <c r="J58" t="s">
         <v>116</v>
       </c>
-      <c r="J58" t="s">
+      <c r="K58" t="s">
         <v>123</v>
       </c>
-      <c r="K58" t="s">
+      <c r="L58" t="s">
         <v>103</v>
       </c>
-      <c r="L58" t="s">
+      <c r="M58" t="s">
         <v>118</v>
       </c>
-      <c r="M58" t="s">
+      <c r="N58" t="s">
         <v>126</v>
       </c>
-      <c r="N58" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O58" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>141</v>
       </c>
@@ -3531,43 +3835,46 @@
         <v>85</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E59" t="s">
+        <v>162</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F59" t="s">
         <v>121</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>125</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
         <v>124</v>
       </c>
-      <c r="H59" t="s">
+      <c r="I59" t="s">
         <v>100</v>
       </c>
-      <c r="I59" t="s">
-        <v>115</v>
-      </c>
       <c r="J59" t="s">
+        <v>115</v>
+      </c>
+      <c r="K59" t="s">
         <v>128</v>
       </c>
-      <c r="K59" t="s">
+      <c r="L59" t="s">
         <v>109</v>
       </c>
-      <c r="L59" t="s">
+      <c r="M59" t="s">
         <v>102</v>
       </c>
-      <c r="M59" t="s">
-        <v>119</v>
-      </c>
       <c r="N59" t="s">
+        <v>119</v>
+      </c>
+      <c r="O59" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>141</v>
       </c>
@@ -3578,40 +3885,43 @@
         <v>149</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E60" t="s">
-        <v>115</v>
+        <v>158</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="F60" t="s">
+        <v>115</v>
+      </c>
+      <c r="G60" t="s">
         <v>120</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>121</v>
       </c>
-      <c r="H60" t="s">
+      <c r="I60" t="s">
         <v>105</v>
       </c>
-      <c r="I60" t="s">
+      <c r="J60" t="s">
         <v>116</v>
       </c>
-      <c r="J60" t="s">
+      <c r="K60" t="s">
         <v>127</v>
       </c>
-      <c r="K60" t="s">
+      <c r="L60" t="s">
         <v>109</v>
       </c>
-      <c r="L60" t="s">
+      <c r="M60" t="s">
         <v>117</v>
       </c>
-      <c r="M60" t="s">
+      <c r="N60" t="s">
         <v>118</v>
       </c>
-      <c r="N60" t="s">
+      <c r="O60" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>141</v>
       </c>
@@ -3619,43 +3929,46 @@
         <v>44</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E61" t="s">
-        <v>115</v>
+        <v>200</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="F61" t="s">
+        <v>115</v>
+      </c>
+      <c r="G61" t="s">
         <v>107</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
         <v>116</v>
       </c>
-      <c r="H61" t="s">
+      <c r="I61" t="s">
         <v>125</v>
       </c>
-      <c r="I61" t="s">
+      <c r="J61" t="s">
         <v>121</v>
       </c>
-      <c r="J61" t="s">
+      <c r="K61" t="s">
         <v>108</v>
       </c>
-      <c r="K61" t="s">
+      <c r="L61" t="s">
         <v>103</v>
       </c>
-      <c r="L61" t="s">
+      <c r="M61" t="s">
         <v>117</v>
       </c>
-      <c r="M61" t="s">
-        <v>119</v>
-      </c>
       <c r="N61" t="s">
+        <v>119</v>
+      </c>
+      <c r="O61" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>141</v>
       </c>
@@ -3663,43 +3976,46 @@
         <v>66</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E62" t="s">
+        <v>168</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F62" t="s">
         <v>116</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>101</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>105</v>
       </c>
-      <c r="H62" t="s">
-        <v>115</v>
-      </c>
       <c r="I62" t="s">
+        <v>115</v>
+      </c>
+      <c r="J62" t="s">
         <v>107</v>
       </c>
-      <c r="J62" t="s">
+      <c r="K62" t="s">
         <v>128</v>
       </c>
-      <c r="K62" t="s">
+      <c r="L62" t="s">
         <v>106</v>
       </c>
-      <c r="L62" t="s">
+      <c r="M62" t="s">
         <v>117</v>
       </c>
-      <c r="M62" t="s">
+      <c r="N62" t="s">
         <v>103</v>
       </c>
-      <c r="N62" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O62" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>141</v>
       </c>
@@ -3710,40 +4026,43 @@
         <v>145</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E63" t="s">
+        <v>159</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F63" t="s">
         <v>116</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>120</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>125</v>
       </c>
-      <c r="H63" t="s">
+      <c r="I63" t="s">
         <v>101</v>
       </c>
-      <c r="I63" t="s">
+      <c r="J63" t="s">
         <v>108</v>
       </c>
-      <c r="J63" t="s">
+      <c r="K63" t="s">
         <v>106</v>
       </c>
-      <c r="K63" t="s">
-        <v>119</v>
-      </c>
       <c r="L63" t="s">
+        <v>119</v>
+      </c>
+      <c r="M63" t="s">
         <v>126</v>
       </c>
-      <c r="M63" t="s">
+      <c r="N63" t="s">
         <v>118</v>
       </c>
-      <c r="N63" t="s">
+      <c r="O63" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>141</v>
       </c>
@@ -3751,43 +4070,46 @@
         <v>89</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>165</v>
+        <v>6</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E64" t="s">
-        <v>115</v>
+        <v>88</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>209</v>
       </c>
       <c r="F64" t="s">
+        <v>115</v>
+      </c>
+      <c r="G64" t="s">
         <v>106</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>100</v>
       </c>
-      <c r="H64" t="s">
+      <c r="I64" t="s">
         <v>101</v>
       </c>
-      <c r="I64" t="s">
+      <c r="J64" t="s">
         <v>116</v>
       </c>
-      <c r="J64" t="s">
+      <c r="K64" t="s">
         <v>102</v>
       </c>
-      <c r="K64" t="s">
-        <v>119</v>
-      </c>
       <c r="L64" t="s">
+        <v>119</v>
+      </c>
+      <c r="M64" t="s">
         <v>109</v>
       </c>
-      <c r="M64" t="s">
+      <c r="N64" t="s">
         <v>122</v>
       </c>
-      <c r="N64" t="s">
+      <c r="O64" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>141</v>
       </c>
@@ -3795,43 +4117,46 @@
         <v>59</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>165</v>
+        <v>4</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E65" t="s">
+        <v>174</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F65" t="s">
         <v>116</v>
       </c>
-      <c r="F65" t="s">
-        <v>115</v>
-      </c>
       <c r="G65" t="s">
+        <v>115</v>
+      </c>
+      <c r="H65" t="s">
         <v>121</v>
       </c>
-      <c r="H65" t="s">
+      <c r="I65" t="s">
         <v>105</v>
       </c>
-      <c r="I65" t="s">
+      <c r="J65" t="s">
         <v>101</v>
       </c>
-      <c r="J65" t="s">
+      <c r="K65" t="s">
         <v>103</v>
       </c>
-      <c r="K65" t="s">
+      <c r="L65" t="s">
         <v>104</v>
       </c>
-      <c r="L65" t="s">
+      <c r="M65" t="s">
         <v>118</v>
       </c>
-      <c r="M65" t="s">
+      <c r="N65" t="s">
         <v>102</v>
       </c>
-      <c r="N65" t="s">
+      <c r="O65" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>141</v>
       </c>
@@ -3839,43 +4164,46 @@
         <v>24</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E66" t="s">
-        <v>115</v>
+        <v>159</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="F66" t="s">
+        <v>115</v>
+      </c>
+      <c r="G66" t="s">
         <v>100</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>121</v>
       </c>
-      <c r="H66" t="s">
+      <c r="I66" t="s">
         <v>128</v>
       </c>
-      <c r="I66" t="s">
+      <c r="J66" t="s">
         <v>120</v>
       </c>
-      <c r="J66" t="s">
+      <c r="K66" t="s">
         <v>106</v>
       </c>
-      <c r="K66" t="s">
+      <c r="L66" t="s">
         <v>108</v>
       </c>
-      <c r="L66" t="s">
+      <c r="M66" t="s">
         <v>130</v>
       </c>
-      <c r="M66" t="s">
+      <c r="N66" t="s">
         <v>103</v>
       </c>
-      <c r="N66" t="s">
+      <c r="O66" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>141</v>
       </c>
@@ -3883,43 +4211,46 @@
         <v>87</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E67" t="s">
+        <v>210</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F67" t="s">
         <v>121</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>120</v>
       </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
         <v>124</v>
       </c>
-      <c r="H67" t="s">
+      <c r="I67" t="s">
         <v>122</v>
       </c>
-      <c r="I67" t="s">
+      <c r="J67" t="s">
         <v>105</v>
       </c>
-      <c r="J67" t="s">
+      <c r="K67" t="s">
         <v>102</v>
       </c>
-      <c r="K67" t="s">
+      <c r="L67" t="s">
         <v>104</v>
       </c>
-      <c r="L67" t="s">
+      <c r="M67" t="s">
         <v>123</v>
       </c>
-      <c r="M67" t="s">
-        <v>119</v>
-      </c>
       <c r="N67" t="s">
+        <v>119</v>
+      </c>
+      <c r="O67" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>141</v>
       </c>
@@ -3930,40 +4261,43 @@
         <v>165</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E68" t="s">
+        <v>166</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F68" t="s">
         <v>121</v>
       </c>
-      <c r="F68" t="s">
+      <c r="G68" t="s">
         <v>116</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>120</v>
       </c>
-      <c r="H68" t="s">
-        <v>115</v>
-      </c>
       <c r="I68" t="s">
+        <v>115</v>
+      </c>
+      <c r="J68" t="s">
         <v>103</v>
       </c>
-      <c r="J68" t="s">
+      <c r="K68" t="s">
         <v>117</v>
       </c>
-      <c r="K68" t="s">
+      <c r="L68" t="s">
         <v>118</v>
       </c>
-      <c r="L68" t="s">
+      <c r="M68" t="s">
         <v>122</v>
       </c>
-      <c r="M68" t="s">
-        <v>119</v>
-      </c>
       <c r="N68" t="s">
+        <v>119</v>
+      </c>
+      <c r="O68" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>141</v>
       </c>
@@ -3971,43 +4305,46 @@
         <v>70</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E69" t="s">
-        <v>115</v>
+        <v>168</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="F69" t="s">
+        <v>115</v>
+      </c>
+      <c r="G69" t="s">
         <v>102</v>
       </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
         <v>120</v>
       </c>
-      <c r="H69" t="s">
+      <c r="I69" t="s">
         <v>126</v>
       </c>
-      <c r="I69" t="s">
+      <c r="J69" t="s">
         <v>106</v>
       </c>
-      <c r="J69" t="s">
+      <c r="K69" t="s">
         <v>100</v>
       </c>
-      <c r="K69" t="s">
+      <c r="L69" t="s">
         <v>121</v>
       </c>
-      <c r="L69" t="s">
+      <c r="M69" t="s">
         <v>103</v>
       </c>
-      <c r="M69" t="s">
+      <c r="N69" t="s">
         <v>117</v>
       </c>
-      <c r="N69" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O69" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>141</v>
       </c>
@@ -4015,43 +4352,46 @@
         <v>41</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>165</v>
+        <v>212</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E70" t="s">
-        <v>115</v>
+        <v>193</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="F70" t="s">
+        <v>115</v>
+      </c>
+      <c r="G70" t="s">
         <v>106</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>127</v>
       </c>
-      <c r="H70" t="s">
+      <c r="I70" t="s">
         <v>109</v>
       </c>
-      <c r="I70" t="s">
+      <c r="J70" t="s">
         <v>123</v>
       </c>
-      <c r="J70" t="s">
+      <c r="K70" t="s">
         <v>118</v>
       </c>
-      <c r="K70" t="s">
-        <v>119</v>
-      </c>
       <c r="L70" t="s">
+        <v>119</v>
+      </c>
+      <c r="M70" t="s">
         <v>125</v>
       </c>
-      <c r="M70" t="s">
+      <c r="N70" t="s">
         <v>126</v>
       </c>
-      <c r="N70" t="s">
+      <c r="O70" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>142</v>
       </c>
@@ -4059,43 +4399,46 @@
         <v>81</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E71" t="s">
+        <v>176</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F71" t="s">
         <v>116</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>120</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
         <v>101</v>
       </c>
-      <c r="H71" t="s">
+      <c r="I71" t="s">
         <v>128</v>
       </c>
-      <c r="I71" t="s">
-        <v>115</v>
-      </c>
       <c r="J71" t="s">
+        <v>115</v>
+      </c>
+      <c r="K71" t="s">
         <v>118</v>
       </c>
-      <c r="K71" t="s">
+      <c r="L71" t="s">
         <v>117</v>
       </c>
-      <c r="L71" t="s">
+      <c r="M71" t="s">
         <v>104</v>
       </c>
-      <c r="M71" t="s">
+      <c r="N71" t="s">
         <v>127</v>
       </c>
-      <c r="N71" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O71" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>142</v>
       </c>
@@ -4103,43 +4446,46 @@
         <v>31</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E72" t="s">
-        <v>115</v>
+        <v>214</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="F72" t="s">
+        <v>115</v>
+      </c>
+      <c r="G72" t="s">
         <v>107</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>125</v>
       </c>
-      <c r="H72" t="s">
+      <c r="I72" t="s">
         <v>121</v>
       </c>
-      <c r="I72" t="s">
+      <c r="J72" t="s">
         <v>126</v>
       </c>
-      <c r="J72" t="s">
+      <c r="K72" t="s">
         <v>128</v>
       </c>
-      <c r="K72" t="s">
+      <c r="L72" t="s">
         <v>103</v>
       </c>
-      <c r="L72" t="s">
+      <c r="M72" t="s">
         <v>109</v>
       </c>
-      <c r="M72" t="s">
-        <v>119</v>
-      </c>
       <c r="N72" t="s">
+        <v>119</v>
+      </c>
+      <c r="O72" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>142</v>
       </c>
@@ -4147,43 +4493,46 @@
         <v>14</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E73" t="s">
-        <v>115</v>
+        <v>158</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="F73" t="s">
+        <v>115</v>
+      </c>
+      <c r="G73" t="s">
         <v>107</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
         <v>122</v>
       </c>
-      <c r="H73" t="s">
+      <c r="I73" t="s">
         <v>105</v>
       </c>
-      <c r="I73" t="s">
+      <c r="J73" t="s">
         <v>100</v>
       </c>
-      <c r="J73" t="s">
+      <c r="K73" t="s">
         <v>108</v>
       </c>
-      <c r="K73" t="s">
-        <v>119</v>
-      </c>
       <c r="L73" t="s">
+        <v>119</v>
+      </c>
+      <c r="M73" t="s">
         <v>126</v>
       </c>
-      <c r="M73" t="s">
+      <c r="N73" t="s">
         <v>109</v>
       </c>
-      <c r="N73" t="s">
+      <c r="O73" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>142</v>
       </c>
@@ -4194,40 +4543,43 @@
         <v>165</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E74" t="s">
+        <v>166</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F74" t="s">
         <v>100</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>121</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
         <v>109</v>
       </c>
-      <c r="H74" t="s">
+      <c r="I74" t="s">
         <v>124</v>
       </c>
-      <c r="I74" t="s">
-        <v>115</v>
-      </c>
       <c r="J74" t="s">
+        <v>115</v>
+      </c>
+      <c r="K74" t="s">
         <v>117</v>
       </c>
-      <c r="K74" t="s">
+      <c r="L74" t="s">
         <v>118</v>
       </c>
-      <c r="L74" t="s">
+      <c r="M74" t="s">
         <v>104</v>
       </c>
-      <c r="M74" t="s">
+      <c r="N74" t="s">
         <v>120</v>
       </c>
-      <c r="N74" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O74" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>142</v>
       </c>
@@ -4238,40 +4590,43 @@
         <v>145</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E75" t="s">
+        <v>159</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F75" t="s">
         <v>107</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>100</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
         <v>104</v>
       </c>
-      <c r="H75" t="s">
+      <c r="I75" t="s">
         <v>124</v>
       </c>
-      <c r="I75" t="s">
+      <c r="J75" t="s">
         <v>102</v>
       </c>
-      <c r="J75" t="s">
+      <c r="K75" t="s">
         <v>127</v>
       </c>
-      <c r="K75" t="s">
+      <c r="L75" t="s">
         <v>122</v>
       </c>
-      <c r="L75" t="s">
+      <c r="M75" t="s">
         <v>117</v>
       </c>
-      <c r="M75" t="s">
+      <c r="N75" t="s">
         <v>118</v>
       </c>
-      <c r="N75" t="s">
+      <c r="O75" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>142</v>
       </c>
@@ -4282,40 +4637,43 @@
         <v>4</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E76" t="s">
-        <v>115</v>
+        <v>174</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="F76" t="s">
+        <v>115</v>
+      </c>
+      <c r="G76" t="s">
         <v>121</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>101</v>
       </c>
-      <c r="H76" t="s">
+      <c r="I76" t="s">
         <v>105</v>
       </c>
-      <c r="I76" t="s">
+      <c r="J76" t="s">
         <v>120</v>
       </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
         <v>102</v>
       </c>
-      <c r="K76" t="s">
+      <c r="L76" t="s">
         <v>109</v>
       </c>
-      <c r="L76" t="s">
+      <c r="M76" t="s">
         <v>104</v>
       </c>
-      <c r="M76" t="s">
+      <c r="N76" t="s">
         <v>117</v>
       </c>
-      <c r="N76" t="s">
+      <c r="O76" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>142</v>
       </c>
@@ -4323,43 +4681,46 @@
         <v>51</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E77" t="s">
-        <v>115</v>
+        <v>159</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="F77" t="s">
+        <v>115</v>
+      </c>
+      <c r="G77" t="s">
         <v>106</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>101</v>
       </c>
-      <c r="H77" t="s">
+      <c r="I77" t="s">
         <v>117</v>
       </c>
-      <c r="I77" t="s">
+      <c r="J77" t="s">
         <v>123</v>
       </c>
-      <c r="J77" t="s">
+      <c r="K77" t="s">
         <v>103</v>
       </c>
-      <c r="K77" t="s">
+      <c r="L77" t="s">
         <v>128</v>
       </c>
-      <c r="L77" t="s">
+      <c r="M77" t="s">
         <v>102</v>
       </c>
-      <c r="M77" t="s">
-        <v>119</v>
-      </c>
       <c r="N77" t="s">
+        <v>119</v>
+      </c>
+      <c r="O77" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>142</v>
       </c>
@@ -4367,43 +4728,46 @@
         <v>53</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E78" t="s">
+        <v>169</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F78" t="s">
         <v>102</v>
       </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>100</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>124</v>
       </c>
-      <c r="H78" t="s">
+      <c r="I78" t="s">
         <v>105</v>
       </c>
-      <c r="I78" t="s">
+      <c r="J78" t="s">
         <v>107</v>
       </c>
-      <c r="J78" t="s">
+      <c r="K78" t="s">
         <v>118</v>
       </c>
-      <c r="K78" t="s">
+      <c r="L78" t="s">
         <v>122</v>
       </c>
-      <c r="L78" t="s">
-        <v>119</v>
-      </c>
       <c r="M78" t="s">
+        <v>119</v>
+      </c>
+      <c r="N78" t="s">
         <v>117</v>
       </c>
-      <c r="N78" t="s">
+      <c r="O78" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>142</v>
       </c>
@@ -4414,40 +4778,43 @@
         <v>152</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E79" t="s">
+        <v>198</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F79" t="s">
         <v>107</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>102</v>
       </c>
-      <c r="G79" t="s">
-        <v>115</v>
-      </c>
       <c r="H79" t="s">
+        <v>115</v>
+      </c>
+      <c r="I79" t="s">
         <v>120</v>
       </c>
-      <c r="I79" t="s">
+      <c r="J79" t="s">
         <v>100</v>
       </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>122</v>
       </c>
-      <c r="K79" t="s">
+      <c r="L79" t="s">
         <v>127</v>
       </c>
-      <c r="L79" t="s">
+      <c r="M79" t="s">
         <v>117</v>
       </c>
-      <c r="M79" t="s">
+      <c r="N79" t="s">
         <v>128</v>
       </c>
-      <c r="N79" t="s">
+      <c r="O79" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>142</v>
       </c>
@@ -4458,40 +4825,43 @@
         <v>4</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E80" t="s">
-        <v>115</v>
+        <v>174</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="F80" t="s">
+        <v>115</v>
+      </c>
+      <c r="G80" t="s">
         <v>125</v>
       </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
         <v>101</v>
       </c>
-      <c r="H80" t="s">
+      <c r="I80" t="s">
         <v>102</v>
       </c>
-      <c r="I80" t="s">
+      <c r="J80" t="s">
         <v>124</v>
       </c>
-      <c r="J80" t="s">
+      <c r="K80" t="s">
         <v>105</v>
       </c>
-      <c r="K80" t="s">
+      <c r="L80" t="s">
         <v>118</v>
       </c>
-      <c r="L80" t="s">
+      <c r="M80" t="s">
         <v>122</v>
       </c>
-      <c r="M80" t="s">
+      <c r="N80" t="s">
         <v>126</v>
       </c>
-      <c r="N80" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O80" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>142</v>
       </c>
@@ -4502,40 +4872,43 @@
         <v>146</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E81" t="s">
+        <v>168</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F81" t="s">
         <v>102</v>
       </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>107</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>120</v>
       </c>
-      <c r="H81" t="s">
+      <c r="I81" t="s">
         <v>101</v>
       </c>
-      <c r="I81" t="s">
+      <c r="J81" t="s">
         <v>109</v>
       </c>
-      <c r="J81" t="s">
+      <c r="K81" t="s">
         <v>118</v>
       </c>
-      <c r="K81" t="s">
+      <c r="L81" t="s">
         <v>128</v>
       </c>
-      <c r="L81" t="s">
+      <c r="M81" t="s">
         <v>121</v>
       </c>
-      <c r="M81" t="s">
+      <c r="N81" t="s">
         <v>127</v>
       </c>
-      <c r="N81" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O81" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>142</v>
       </c>
@@ -4543,43 +4916,46 @@
         <v>25</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E82" t="s">
+        <v>173</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F82" t="s">
         <v>121</v>
       </c>
-      <c r="F82" t="s">
-        <v>115</v>
-      </c>
       <c r="G82" t="s">
+        <v>115</v>
+      </c>
+      <c r="H82" t="s">
         <v>120</v>
       </c>
-      <c r="H82" t="s">
+      <c r="I82" t="s">
         <v>105</v>
       </c>
-      <c r="I82" t="s">
+      <c r="J82" t="s">
         <v>116</v>
       </c>
-      <c r="J82" t="s">
+      <c r="K82" t="s">
         <v>104</v>
       </c>
-      <c r="K82" t="s">
+      <c r="L82" t="s">
         <v>124</v>
       </c>
-      <c r="L82" t="s">
+      <c r="M82" t="s">
         <v>127</v>
       </c>
-      <c r="M82" t="s">
+      <c r="N82" t="s">
         <v>102</v>
       </c>
-      <c r="N82" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O82" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>142</v>
       </c>
@@ -4587,43 +4963,46 @@
         <v>82</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E83" t="s">
+        <v>176</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F83" t="s">
         <v>100</v>
       </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>127</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>103</v>
       </c>
-      <c r="H83" t="s">
+      <c r="I83" t="s">
         <v>118</v>
       </c>
-      <c r="I83" t="s">
+      <c r="J83" t="s">
         <v>105</v>
       </c>
-      <c r="J83" t="s">
+      <c r="K83" t="s">
         <v>126</v>
       </c>
-      <c r="K83" t="s">
+      <c r="L83" t="s">
         <v>120</v>
       </c>
-      <c r="L83" t="s">
+      <c r="M83" t="s">
         <v>116</v>
       </c>
-      <c r="M83" t="s">
-        <v>119</v>
-      </c>
       <c r="N83" t="s">
+        <v>119</v>
+      </c>
+      <c r="O83" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>142</v>
       </c>
@@ -4631,43 +5010,46 @@
         <v>13</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>165</v>
+        <v>3</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E84" t="s">
-        <v>115</v>
+        <v>203</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>189</v>
       </c>
       <c r="F84" t="s">
+        <v>115</v>
+      </c>
+      <c r="G84" t="s">
         <v>100</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>121</v>
       </c>
-      <c r="H84" t="s">
+      <c r="I84" t="s">
         <v>126</v>
       </c>
-      <c r="I84" t="s">
+      <c r="J84" t="s">
         <v>122</v>
       </c>
-      <c r="J84" t="s">
+      <c r="K84" t="s">
         <v>106</v>
       </c>
-      <c r="K84" t="s">
+      <c r="L84" t="s">
         <v>103</v>
       </c>
-      <c r="L84" t="s">
+      <c r="M84" t="s">
         <v>128</v>
       </c>
-      <c r="M84" t="s">
+      <c r="N84" t="s">
         <v>102</v>
       </c>
-      <c r="N84" t="s">
+      <c r="O84" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>142</v>
       </c>
@@ -4675,43 +5057,46 @@
         <v>45</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E85" t="s">
+        <v>200</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F85" t="s">
         <v>105</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>125</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>121</v>
       </c>
-      <c r="H85" t="s">
+      <c r="I85" t="s">
         <v>103</v>
       </c>
-      <c r="I85" t="s">
+      <c r="J85" t="s">
         <v>118</v>
       </c>
-      <c r="J85" t="s">
-        <v>119</v>
-      </c>
       <c r="K85" t="s">
+        <v>119</v>
+      </c>
+      <c r="L85" t="s">
         <v>126</v>
       </c>
-      <c r="L85" t="s">
+      <c r="M85" t="s">
         <v>108</v>
       </c>
-      <c r="M85" t="s">
+      <c r="N85" t="s">
         <v>117</v>
       </c>
-      <c r="N85" t="s">
+      <c r="O85" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>142</v>
       </c>
@@ -4722,40 +5107,43 @@
         <v>2</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E86" t="s">
-        <v>115</v>
+        <v>193</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="F86" t="s">
+        <v>115</v>
+      </c>
+      <c r="G86" t="s">
         <v>120</v>
       </c>
-      <c r="G86" t="s">
+      <c r="H86" t="s">
         <v>108</v>
       </c>
-      <c r="H86" t="s">
+      <c r="I86" t="s">
         <v>121</v>
       </c>
-      <c r="I86" t="s">
+      <c r="J86" t="s">
         <v>116</v>
       </c>
-      <c r="J86" t="s">
+      <c r="K86" t="s">
         <v>126</v>
       </c>
-      <c r="K86" t="s">
+      <c r="L86" t="s">
         <v>109</v>
       </c>
-      <c r="L86" t="s">
+      <c r="M86" t="s">
         <v>118</v>
       </c>
-      <c r="M86" t="s">
+      <c r="N86" t="s">
         <v>104</v>
       </c>
-      <c r="N86" t="s">
+      <c r="O86" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>142</v>
       </c>
@@ -4763,44 +5151,47 @@
         <v>68</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E87" t="s">
+        <v>168</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F87" t="s">
         <v>102</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>100</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
         <v>121</v>
       </c>
-      <c r="H87" t="s">
-        <v>115</v>
-      </c>
       <c r="I87" t="s">
+        <v>115</v>
+      </c>
+      <c r="J87" t="s">
         <v>106</v>
       </c>
-      <c r="J87" t="s">
+      <c r="K87" t="s">
         <v>122</v>
       </c>
-      <c r="K87" t="s">
+      <c r="L87" t="s">
         <v>101</v>
       </c>
-      <c r="L87" t="s">
+      <c r="M87" t="s">
         <v>126</v>
       </c>
-      <c r="M87" t="s">
+      <c r="N87" t="s">
         <v>116</v>
       </c>
-      <c r="N87" t="s">
+      <c r="O87" t="s">
         <v>120</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:N18">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:O18">
     <sortCondition ref="B2:B18"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/TREINAMENTO_ FORCAS_QUIPES_BD.xlsx
+++ b/TREINAMENTO_ FORCAS_QUIPES_BD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ELYOMIDSON.BRANDAO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A7EA92-BE58-4883-8A66-2521A9F2C00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF795603-D16C-4268-BB2F-D39AF9DF107B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2C811CF7-C894-4D80-8AC2-C4C3C914DEBA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="216">
   <si>
     <t>TI</t>
   </si>
@@ -504,9 +504,6 @@
   </si>
   <si>
     <t>Pecuaria</t>
-  </si>
-  <si>
-    <t>Validar Setor</t>
   </si>
   <si>
     <t>Gestor</t>
@@ -1112,7 +1109,7 @@
         <v>143</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>144</v>
@@ -1159,7 +1156,7 @@
         <v>147</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>153</v>
@@ -1209,7 +1206,7 @@
         <v>88</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F3" t="s">
         <v>120</v>
@@ -1250,13 +1247,13 @@
         <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F4" t="s">
         <v>102</v>
@@ -1297,13 +1294,13 @@
         <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F5" t="s">
         <v>121</v>
@@ -1347,10 +1344,10 @@
         <v>148</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F6" t="s">
         <v>116</v>
@@ -1394,10 +1391,10 @@
         <v>149</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F7" t="s">
         <v>107</v>
@@ -1441,10 +1438,10 @@
         <v>150</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F8" t="s">
         <v>126</v>
@@ -1485,13 +1482,13 @@
         <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F9" t="s">
         <v>120</v>
@@ -1535,10 +1532,10 @@
         <v>155</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F10" t="s">
         <v>100</v>
@@ -1579,13 +1576,13 @@
         <v>74</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="E11" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F11" t="s">
         <v>115</v>
@@ -1626,13 +1623,13 @@
         <v>62</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="E12" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F12" t="s">
         <v>119</v>
@@ -1676,10 +1673,10 @@
         <v>154</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F13" t="s">
         <v>123</v>
@@ -1726,7 +1723,7 @@
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F14" t="s">
         <v>115</v>
@@ -1770,10 +1767,10 @@
         <v>5</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F15" t="s">
         <v>120</v>
@@ -1814,13 +1811,13 @@
         <v>92</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F16" t="s">
         <v>125</v>
@@ -1864,10 +1861,10 @@
         <v>4</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F17" t="s">
         <v>115</v>
@@ -1911,10 +1908,10 @@
         <v>145</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F18" t="s">
         <v>106</v>
@@ -1958,10 +1955,10 @@
         <v>146</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F19" t="s">
         <v>127</v>
@@ -2008,7 +2005,7 @@
         <v>86</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F20" t="s">
         <v>115</v>
@@ -2049,13 +2046,13 @@
         <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F21" t="s">
         <v>115</v>
@@ -2096,13 +2093,13 @@
         <v>79</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F22" t="s">
         <v>115</v>
@@ -2143,13 +2140,13 @@
         <v>64</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="F23" t="s">
         <v>106</v>
@@ -2190,13 +2187,13 @@
         <v>75</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F24" t="s">
         <v>115</v>
@@ -2240,10 +2237,10 @@
         <v>1</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F25" t="s">
         <v>107</v>
@@ -2284,13 +2281,13 @@
         <v>19</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F26" t="s">
         <v>102</v>
@@ -2334,10 +2331,10 @@
         <v>0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F27" t="s">
         <v>105</v>
@@ -2381,10 +2378,10 @@
         <v>151</v>
       </c>
       <c r="D28" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="F28" t="s">
         <v>115</v>
@@ -2431,7 +2428,7 @@
         <v>10</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F29" t="s">
         <v>115</v>
@@ -2475,10 +2472,10 @@
         <v>147</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F30" t="s">
         <v>115</v>
@@ -2522,10 +2519,10 @@
         <v>5</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F31" t="s">
         <v>127</v>
@@ -2569,10 +2566,10 @@
         <v>2</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F32" t="s">
         <v>115</v>
@@ -2616,10 +2613,10 @@
         <v>149</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F33" t="s">
         <v>100</v>
@@ -2660,13 +2657,13 @@
         <v>80</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="E34" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F34" t="s">
         <v>120</v>
@@ -2710,10 +2707,10 @@
         <v>145</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F35" t="s">
         <v>121</v>
@@ -2757,10 +2754,10 @@
         <v>4</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F36" t="s">
         <v>100</v>
@@ -2804,10 +2801,10 @@
         <v>7</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F37" t="s">
         <v>121</v>
@@ -2851,10 +2848,10 @@
         <v>6</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F38" t="s">
         <v>116</v>
@@ -2895,13 +2892,13 @@
         <v>69</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="F39" t="s">
         <v>107</v>
@@ -2945,10 +2942,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F40" t="s">
         <v>100</v>
@@ -2989,13 +2986,13 @@
         <v>23</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F41" t="s">
         <v>120</v>
@@ -3036,13 +3033,13 @@
         <v>65</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F42" t="s">
         <v>115</v>
@@ -3086,10 +3083,10 @@
         <v>0</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F43" t="s">
         <v>105</v>
@@ -3133,10 +3130,10 @@
         <v>154</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F44" t="s">
         <v>124</v>
@@ -3177,13 +3174,13 @@
         <v>43</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="E45" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F45" t="s">
         <v>115</v>
@@ -3227,10 +3224,10 @@
         <v>4</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F46" t="s">
         <v>121</v>
@@ -3274,10 +3271,10 @@
         <v>1</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F47" t="s">
         <v>100</v>
@@ -3321,10 +3318,10 @@
         <v>5</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F48" t="s">
         <v>100</v>
@@ -3365,13 +3362,13 @@
         <v>33</v>
       </c>
       <c r="C49" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="F49" t="s">
         <v>121</v>
@@ -3415,10 +3412,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F50" t="s">
         <v>100</v>
@@ -3462,10 +3459,10 @@
         <v>149</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F51" t="s">
         <v>107</v>
@@ -3506,13 +3503,13 @@
         <v>76</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="E52" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F52" t="s">
         <v>122</v>
@@ -3556,10 +3553,10 @@
         <v>145</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F53" t="s">
         <v>115</v>
@@ -3603,10 +3600,10 @@
         <v>152</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" t="s">
         <v>102</v>
@@ -3650,10 +3647,10 @@
         <v>1</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F55" t="s">
         <v>115</v>
@@ -3697,10 +3694,10 @@
         <v>0</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F56" t="s">
         <v>125</v>
@@ -3741,13 +3738,13 @@
         <v>91</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>92</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F57" t="s">
         <v>115</v>
@@ -3788,13 +3785,13 @@
         <v>84</v>
       </c>
       <c r="C58" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="F58" t="s">
         <v>115</v>
@@ -3835,13 +3832,13 @@
         <v>85</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F59" t="s">
         <v>121</v>
@@ -3885,10 +3882,10 @@
         <v>149</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F60" t="s">
         <v>115</v>
@@ -3929,13 +3926,13 @@
         <v>44</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F61" t="s">
         <v>115</v>
@@ -3979,10 +3976,10 @@
         <v>146</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F62" t="s">
         <v>116</v>
@@ -4026,10 +4023,10 @@
         <v>145</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F63" t="s">
         <v>116</v>
@@ -4076,7 +4073,7 @@
         <v>88</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F64" t="s">
         <v>115</v>
@@ -4120,10 +4117,10 @@
         <v>4</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F65" t="s">
         <v>116</v>
@@ -4164,13 +4161,13 @@
         <v>24</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F66" t="s">
         <v>115</v>
@@ -4211,13 +4208,13 @@
         <v>87</v>
       </c>
       <c r="C67" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="F67" t="s">
         <v>121</v>
@@ -4258,13 +4255,13 @@
         <v>77</v>
       </c>
       <c r="C68" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="E68" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F68" t="s">
         <v>121</v>
@@ -4305,13 +4302,13 @@
         <v>70</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="F69" t="s">
         <v>115</v>
@@ -4352,13 +4349,13 @@
         <v>41</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F70" t="s">
         <v>115</v>
@@ -4399,13 +4396,13 @@
         <v>81</v>
       </c>
       <c r="C71" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="E71" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F71" t="s">
         <v>116</v>
@@ -4446,13 +4443,13 @@
         <v>31</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="E72" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F72" t="s">
         <v>115</v>
@@ -4493,13 +4490,13 @@
         <v>14</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F73" t="s">
         <v>115</v>
@@ -4540,13 +4537,13 @@
         <v>78</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="E74" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F74" t="s">
         <v>100</v>
@@ -4590,10 +4587,10 @@
         <v>145</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F75" t="s">
         <v>107</v>
@@ -4637,10 +4634,10 @@
         <v>4</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F76" t="s">
         <v>115</v>
@@ -4681,13 +4678,13 @@
         <v>51</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F77" t="s">
         <v>115</v>
@@ -4731,10 +4728,10 @@
         <v>154</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F78" t="s">
         <v>102</v>
@@ -4778,10 +4775,10 @@
         <v>152</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F79" t="s">
         <v>107</v>
@@ -4825,10 +4822,10 @@
         <v>4</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F80" t="s">
         <v>115</v>
@@ -4872,10 +4869,10 @@
         <v>146</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F81" t="s">
         <v>102</v>
@@ -4916,13 +4913,13 @@
         <v>25</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F82" t="s">
         <v>121</v>
@@ -4963,13 +4960,13 @@
         <v>82</v>
       </c>
       <c r="C83" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="E83" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F83" t="s">
         <v>100</v>
@@ -5013,10 +5010,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F84" t="s">
         <v>115</v>
@@ -5057,13 +5054,13 @@
         <v>45</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F85" t="s">
         <v>105</v>
@@ -5107,10 +5104,10 @@
         <v>2</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F86" t="s">
         <v>115</v>
@@ -5151,13 +5148,13 @@
         <v>68</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F87" t="s">
         <v>102</v>

--- a/TREINAMENTO_ FORCAS_QUIPES_BD.xlsx
+++ b/TREINAMENTO_ FORCAS_QUIPES_BD.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ELYOMIDSON.BRANDAO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupocanel-my.sharepoint.com/personal/elyomidson_brandao_canel_com_br/Documents/Documentos/python-projetos/TREINAMENTO FORCA EQUIPE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF795603-D16C-4268-BB2F-D39AF9DF107B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{CF795603-D16C-4268-BB2F-D39AF9DF107B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{103BA343-6A49-4688-BCD7-71AD21A37A13}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2C811CF7-C894-4D80-8AC2-C4C3C914DEBA}"/>
   </bookViews>
   <sheets>
     <sheet name="TURMAS" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TURMAS!$F$1:$J$84</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="209">
   <si>
     <t>TI</t>
   </si>
@@ -131,9 +134,6 @@
     <t>Kayllane</t>
   </si>
   <si>
-    <t>Afonso</t>
-  </si>
-  <si>
     <t>Jayna</t>
   </si>
   <si>
@@ -290,12 +290,6 @@
     <t>Gleison</t>
   </si>
   <si>
-    <t>Gleide</t>
-  </si>
-  <si>
-    <t>Josivaldo</t>
-  </si>
-  <si>
     <t>Denis</t>
   </si>
   <si>
@@ -338,9 +332,6 @@
     <t>Top 5</t>
   </si>
   <si>
-    <t>Justiça</t>
-  </si>
-  <si>
     <t>Esperança</t>
   </si>
   <si>
@@ -650,12 +641,6 @@
     <t>Comprador</t>
   </si>
   <si>
-    <t>Usina</t>
-  </si>
-  <si>
-    <t>Operaodor de Moinho</t>
-  </si>
-  <si>
     <t>Mecânico Industrial</t>
   </si>
   <si>
@@ -674,23 +659,20 @@
     <t>Marketing</t>
   </si>
   <si>
-    <t>Escritório Teresina</t>
-  </si>
-  <si>
-    <t>Diretoria</t>
-  </si>
-  <si>
     <t>DGP</t>
   </si>
   <si>
     <t>Almoxarifado Graúna</t>
+  </si>
+  <si>
+    <t>Justiça (Imparcialidade)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -709,6 +691,23 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -740,13 +739,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1081,7 +1083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA46323A-AC17-4915-8B32-290002EF3BA9}">
-  <dimension ref="A1:O87"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.21875" customWidth="1"/>
@@ -1096,622 +1098,630 @@
     <col min="12" max="12" width="17.33203125" customWidth="1"/>
     <col min="13" max="14" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="21.33203125" customWidth="1"/>
+    <col min="17" max="17" width="20.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="R1">
+        <f>COUNTIF(F:J,Q1)</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="D2" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J2" t="s">
         <v>97</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="K2" t="s">
+        <v>126</v>
+      </c>
+      <c r="L2" t="s">
         <v>113</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="M2" t="s">
+        <v>100</v>
+      </c>
+      <c r="N2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J2" t="s">
-        <v>101</v>
-      </c>
-      <c r="K2" t="s">
-        <v>130</v>
-      </c>
-      <c r="L2" t="s">
-        <v>117</v>
-      </c>
-      <c r="M2" t="s">
-        <v>104</v>
-      </c>
-      <c r="N2" t="s">
-        <v>118</v>
-      </c>
       <c r="O2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="K3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="L3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="M3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="N3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I4" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="J4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="K4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="M4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="N4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G5" t="s">
+        <v>111</v>
+      </c>
+      <c r="H5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I5" t="s">
+        <v>103</v>
+      </c>
+      <c r="J5" t="s">
+        <v>127</v>
+      </c>
+      <c r="K5" t="s">
+        <v>99</v>
+      </c>
+      <c r="L5" t="s">
+        <v>114</v>
+      </c>
+      <c r="M5" t="s">
+        <v>122</v>
+      </c>
+      <c r="N5" t="s">
+        <v>105</v>
+      </c>
+      <c r="O5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H6" t="s">
         <v>121</v>
       </c>
-      <c r="G5" t="s">
-        <v>115</v>
-      </c>
-      <c r="H5" t="s">
-        <v>101</v>
-      </c>
-      <c r="I5" t="s">
-        <v>107</v>
-      </c>
-      <c r="J5" t="s">
-        <v>131</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="I6" t="s">
         <v>103</v>
       </c>
-      <c r="L5" t="s">
+      <c r="J6" t="s">
+        <v>111</v>
+      </c>
+      <c r="K6" t="s">
+        <v>119</v>
+      </c>
+      <c r="L6" t="s">
+        <v>114</v>
+      </c>
+      <c r="M6" t="s">
         <v>118</v>
       </c>
-      <c r="M5" t="s">
-        <v>126</v>
-      </c>
-      <c r="N5" t="s">
-        <v>109</v>
-      </c>
-      <c r="O5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G6" t="s">
-        <v>120</v>
-      </c>
-      <c r="H6" t="s">
-        <v>125</v>
-      </c>
-      <c r="I6" t="s">
-        <v>107</v>
-      </c>
-      <c r="J6" t="s">
-        <v>115</v>
-      </c>
-      <c r="K6" t="s">
-        <v>123</v>
-      </c>
-      <c r="L6" t="s">
-        <v>118</v>
-      </c>
-      <c r="M6" t="s">
-        <v>122</v>
-      </c>
       <c r="N6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="O6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" t="s">
+        <v>121</v>
+      </c>
+      <c r="H7" t="s">
+        <v>104</v>
+      </c>
+      <c r="I7" t="s">
+        <v>124</v>
+      </c>
+      <c r="J7" t="s">
+        <v>115</v>
+      </c>
+      <c r="K7" t="s">
+        <v>113</v>
+      </c>
+      <c r="L7" t="s">
+        <v>105</v>
+      </c>
+      <c r="M7" t="s">
+        <v>127</v>
+      </c>
+      <c r="N7" t="s">
+        <v>119</v>
+      </c>
+      <c r="O7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F7" t="s">
-        <v>107</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="E8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F8" t="s">
+        <v>122</v>
+      </c>
+      <c r="G8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" t="s">
+        <v>103</v>
+      </c>
+      <c r="I8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J8" t="s">
+        <v>121</v>
+      </c>
+      <c r="K8" t="s">
+        <v>102</v>
+      </c>
+      <c r="L8" t="s">
+        <v>105</v>
+      </c>
+      <c r="M8" t="s">
+        <v>113</v>
+      </c>
+      <c r="N8" t="s">
+        <v>119</v>
+      </c>
+      <c r="O8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F9" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" t="s">
+        <v>111</v>
+      </c>
+      <c r="H9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I9" t="s">
+        <v>117</v>
+      </c>
+      <c r="J9" t="s">
+        <v>101</v>
+      </c>
+      <c r="K9" t="s">
+        <v>97</v>
+      </c>
+      <c r="L9" t="s">
+        <v>105</v>
+      </c>
+      <c r="M9" t="s">
+        <v>127</v>
+      </c>
+      <c r="N9" t="s">
+        <v>98</v>
+      </c>
+      <c r="O9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10" t="s">
+        <v>115</v>
+      </c>
+      <c r="I10" t="s">
+        <v>126</v>
+      </c>
+      <c r="J10" t="s">
+        <v>104</v>
+      </c>
+      <c r="K10" t="s">
+        <v>118</v>
+      </c>
+      <c r="L10" t="s">
+        <v>102</v>
+      </c>
+      <c r="M10" t="s">
+        <v>105</v>
+      </c>
+      <c r="N10" t="s">
+        <v>114</v>
+      </c>
+      <c r="O10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F11" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" t="s">
+        <v>208</v>
+      </c>
+      <c r="H11" t="s">
         <v>125</v>
       </c>
-      <c r="H7" t="s">
-        <v>108</v>
-      </c>
-      <c r="I7" t="s">
-        <v>128</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="I11" t="s">
+        <v>118</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K11" t="s">
+        <v>126</v>
+      </c>
+      <c r="L11" t="s">
+        <v>113</v>
+      </c>
+      <c r="M11" t="s">
         <v>119</v>
       </c>
-      <c r="K7" t="s">
+      <c r="N11" t="s">
+        <v>127</v>
+      </c>
+      <c r="O11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G12" t="s">
+        <v>123</v>
+      </c>
+      <c r="H12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J12" t="s">
+        <v>102</v>
+      </c>
+      <c r="K12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" t="s">
+        <v>121</v>
+      </c>
+      <c r="M12" t="s">
+        <v>127</v>
+      </c>
+      <c r="N12" t="s">
+        <v>124</v>
+      </c>
+      <c r="O12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G13" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" t="s">
+        <v>208</v>
+      </c>
+      <c r="I13" t="s">
         <v>117</v>
       </c>
-      <c r="L7" t="s">
-        <v>109</v>
-      </c>
-      <c r="M7" t="s">
-        <v>131</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="J13" t="s">
+        <v>97</v>
+      </c>
+      <c r="K13" t="s">
+        <v>114</v>
+      </c>
+      <c r="L13" t="s">
+        <v>113</v>
+      </c>
+      <c r="M13" t="s">
+        <v>115</v>
+      </c>
+      <c r="N13" t="s">
         <v>123</v>
       </c>
-      <c r="O7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F8" t="s">
-        <v>126</v>
-      </c>
-      <c r="G8" t="s">
-        <v>115</v>
-      </c>
-      <c r="H8" t="s">
-        <v>107</v>
-      </c>
-      <c r="I8" t="s">
-        <v>100</v>
-      </c>
-      <c r="J8" t="s">
-        <v>125</v>
-      </c>
-      <c r="K8" t="s">
-        <v>106</v>
-      </c>
-      <c r="L8" t="s">
-        <v>109</v>
-      </c>
-      <c r="M8" t="s">
-        <v>117</v>
-      </c>
-      <c r="N8" t="s">
-        <v>123</v>
-      </c>
-      <c r="O8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>138</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G9" t="s">
-        <v>115</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="O13" t="s">
         <v>122</v>
       </c>
-      <c r="I9" t="s">
-        <v>121</v>
-      </c>
-      <c r="J9" t="s">
-        <v>105</v>
-      </c>
-      <c r="K9" t="s">
-        <v>101</v>
-      </c>
-      <c r="L9" t="s">
-        <v>109</v>
-      </c>
-      <c r="M9" t="s">
-        <v>131</v>
-      </c>
-      <c r="N9" t="s">
-        <v>102</v>
-      </c>
-      <c r="O9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>138</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="F10" t="s">
-        <v>100</v>
-      </c>
-      <c r="G10" t="s">
-        <v>107</v>
-      </c>
-      <c r="H10" t="s">
-        <v>119</v>
-      </c>
-      <c r="I10" t="s">
-        <v>130</v>
-      </c>
-      <c r="J10" t="s">
-        <v>108</v>
-      </c>
-      <c r="K10" t="s">
-        <v>122</v>
-      </c>
-      <c r="L10" t="s">
-        <v>106</v>
-      </c>
-      <c r="M10" t="s">
-        <v>109</v>
-      </c>
-      <c r="N10" t="s">
-        <v>118</v>
-      </c>
-      <c r="O10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>138</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="F11" t="s">
-        <v>115</v>
-      </c>
-      <c r="G11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H11" t="s">
-        <v>129</v>
-      </c>
-      <c r="I11" t="s">
-        <v>122</v>
-      </c>
-      <c r="J11" t="s">
-        <v>105</v>
-      </c>
-      <c r="K11" t="s">
-        <v>130</v>
-      </c>
-      <c r="L11" t="s">
-        <v>117</v>
-      </c>
-      <c r="M11" t="s">
-        <v>123</v>
-      </c>
-      <c r="N11" t="s">
-        <v>131</v>
-      </c>
-      <c r="O11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>138</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="F12" t="s">
-        <v>119</v>
-      </c>
-      <c r="G12" t="s">
-        <v>127</v>
-      </c>
-      <c r="H12" t="s">
-        <v>103</v>
-      </c>
-      <c r="I12" t="s">
-        <v>109</v>
-      </c>
-      <c r="J12" t="s">
-        <v>106</v>
-      </c>
-      <c r="K12" t="s">
-        <v>107</v>
-      </c>
-      <c r="L12" t="s">
-        <v>125</v>
-      </c>
-      <c r="M12" t="s">
-        <v>131</v>
-      </c>
-      <c r="N12" t="s">
-        <v>128</v>
-      </c>
-      <c r="O12" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>138</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="F13" t="s">
-        <v>123</v>
-      </c>
-      <c r="G13" t="s">
-        <v>107</v>
-      </c>
-      <c r="H13" t="s">
-        <v>100</v>
-      </c>
-      <c r="I13" t="s">
-        <v>121</v>
-      </c>
-      <c r="J13" t="s">
-        <v>101</v>
-      </c>
-      <c r="K13" t="s">
-        <v>118</v>
-      </c>
-      <c r="L13" t="s">
-        <v>117</v>
-      </c>
-      <c r="M13" t="s">
-        <v>119</v>
-      </c>
-      <c r="N13" t="s">
-        <v>127</v>
-      </c>
-      <c r="O13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
@@ -1723,277 +1733,277 @@
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F14" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G14" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J14" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="K14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L14" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="M14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N14" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="O14" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F15" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I15" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J15" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K15" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L15" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="M15" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="N15" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="O15" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16" t="s">
+        <v>121</v>
+      </c>
+      <c r="G16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" t="s">
+        <v>112</v>
+      </c>
+      <c r="I16" t="s">
+        <v>97</v>
+      </c>
+      <c r="J16" t="s">
+        <v>208</v>
+      </c>
+      <c r="K16" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>138</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F16" t="s">
-        <v>125</v>
-      </c>
-      <c r="G16" t="s">
-        <v>115</v>
-      </c>
-      <c r="H16" t="s">
-        <v>116</v>
-      </c>
-      <c r="I16" t="s">
-        <v>101</v>
-      </c>
-      <c r="J16" t="s">
-        <v>100</v>
-      </c>
-      <c r="K16" t="s">
-        <v>123</v>
-      </c>
       <c r="L16" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="M16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N16" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O16" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F17" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G17" t="s">
-        <v>100</v>
+        <v>208</v>
       </c>
       <c r="H17" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I17" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="K17" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M17" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="N17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="O17" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F18" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G18" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H18" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I18" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J18" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="K18" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="L18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="M18" t="s">
-        <v>100</v>
+        <v>208</v>
       </c>
       <c r="N18" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F19" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G19" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H19" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I19" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J19" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="K19" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L19" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="M19" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N19" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O19" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>12</v>
@@ -2002,421 +2012,421 @@
         <v>3</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>86</v>
+        <v>198</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F20" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G20" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H20" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I20" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J20" t="s">
+        <v>114</v>
+      </c>
+      <c r="K20" t="s">
+        <v>99</v>
+      </c>
+      <c r="L20" t="s">
+        <v>113</v>
+      </c>
+      <c r="M20" t="s">
         <v>118</v>
       </c>
-      <c r="K20" t="s">
-        <v>103</v>
-      </c>
-      <c r="L20" t="s">
-        <v>117</v>
-      </c>
-      <c r="M20" t="s">
-        <v>122</v>
-      </c>
       <c r="N20" t="s">
+        <v>115</v>
+      </c>
+      <c r="O20" t="s">
         <v>119</v>
-      </c>
-      <c r="O20" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F21" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G21" t="s">
-        <v>100</v>
+        <v>208</v>
       </c>
       <c r="H21" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I21" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J21" t="s">
+        <v>118</v>
+      </c>
+      <c r="K21" t="s">
         <v>122</v>
       </c>
-      <c r="K21" t="s">
-        <v>126</v>
-      </c>
       <c r="L21" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="M21" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="N21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="O21" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F22" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G22" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H22" t="s">
+        <v>112</v>
+      </c>
+      <c r="I22" t="s">
+        <v>98</v>
+      </c>
+      <c r="J22" t="s">
         <v>116</v>
       </c>
-      <c r="I22" t="s">
-        <v>102</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
+        <v>114</v>
+      </c>
+      <c r="L22" t="s">
         <v>120</v>
       </c>
-      <c r="K22" t="s">
+      <c r="M22" t="s">
         <v>118</v>
       </c>
-      <c r="L22" t="s">
+      <c r="N22" t="s">
+        <v>101</v>
+      </c>
+      <c r="O22" t="s">
         <v>124</v>
-      </c>
-      <c r="M22" t="s">
-        <v>122</v>
-      </c>
-      <c r="N22" t="s">
-        <v>105</v>
-      </c>
-      <c r="O22" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F23" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G23" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H23" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I23" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="J23" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K23" t="s">
+        <v>115</v>
+      </c>
+      <c r="L23" t="s">
+        <v>113</v>
+      </c>
+      <c r="M23" t="s">
         <v>119</v>
       </c>
-      <c r="L23" t="s">
-        <v>117</v>
-      </c>
-      <c r="M23" t="s">
-        <v>123</v>
-      </c>
       <c r="N23" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O23" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F24" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G24" t="s">
+        <v>112</v>
+      </c>
+      <c r="H24" t="s">
         <v>116</v>
       </c>
-      <c r="H24" t="s">
-        <v>120</v>
-      </c>
       <c r="I24" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="J24" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K24" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="L24" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M24" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N24" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="O24" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F25" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G25" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H25" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="I25" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J25" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="K25" t="s">
+        <v>114</v>
+      </c>
+      <c r="L25" t="s">
         <v>118</v>
       </c>
-      <c r="L25" t="s">
-        <v>122</v>
-      </c>
       <c r="M25" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N25" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="O25" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F26" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G26" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H26" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I26" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J26" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K26" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="L26" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M26" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="N26" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O26" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F27" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G27" t="s">
+        <v>116</v>
+      </c>
+      <c r="H27" t="s">
+        <v>130</v>
+      </c>
+      <c r="I27" t="s">
+        <v>104</v>
+      </c>
+      <c r="J27" t="s">
+        <v>117</v>
+      </c>
+      <c r="K27" t="s">
         <v>120</v>
       </c>
-      <c r="H27" t="s">
-        <v>134</v>
-      </c>
-      <c r="I27" t="s">
-        <v>108</v>
-      </c>
-      <c r="J27" t="s">
-        <v>121</v>
-      </c>
-      <c r="K27" t="s">
-        <v>124</v>
-      </c>
       <c r="L27" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="M27" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="N27" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O27" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F28" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G28" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H28" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I28" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J28" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K28" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L28" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="M28" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="N28" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O28" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>9</v>
@@ -2428,371 +2438,371 @@
         <v>10</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F29" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G29" t="s">
+        <v>208</v>
+      </c>
+      <c r="H29" t="s">
+        <v>120</v>
+      </c>
+      <c r="I29" t="s">
+        <v>130</v>
+      </c>
+      <c r="J29" t="s">
+        <v>121</v>
+      </c>
+      <c r="K29" t="s">
+        <v>124</v>
+      </c>
+      <c r="L29" t="s">
+        <v>103</v>
+      </c>
+      <c r="M29" t="s">
+        <v>98</v>
+      </c>
+      <c r="N29" t="s">
+        <v>122</v>
+      </c>
+      <c r="O29" t="s">
         <v>100</v>
-      </c>
-      <c r="H29" t="s">
-        <v>124</v>
-      </c>
-      <c r="I29" t="s">
-        <v>134</v>
-      </c>
-      <c r="J29" t="s">
-        <v>125</v>
-      </c>
-      <c r="K29" t="s">
-        <v>128</v>
-      </c>
-      <c r="L29" t="s">
-        <v>107</v>
-      </c>
-      <c r="M29" t="s">
-        <v>102</v>
-      </c>
-      <c r="N29" t="s">
-        <v>126</v>
-      </c>
-      <c r="O29" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F30" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G30" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H30" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I30" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J30" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K30" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="L30" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M30" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N30" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="O30" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F31" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G31" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H31" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I31" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J31" t="s">
-        <v>100</v>
+        <v>208</v>
       </c>
       <c r="K31" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="L31" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M31" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N31" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O31" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F32" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G32" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H32" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I32" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J32" t="s">
-        <v>100</v>
+        <v>208</v>
       </c>
       <c r="K32" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L32" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M32" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N32" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O32" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F33" t="s">
+        <v>208</v>
+      </c>
+      <c r="G33" t="s">
+        <v>97</v>
+      </c>
+      <c r="H33" t="s">
+        <v>98</v>
+      </c>
+      <c r="I33" t="s">
+        <v>99</v>
+      </c>
+      <c r="J33" t="s">
         <v>100</v>
       </c>
-      <c r="G33" t="s">
-        <v>101</v>
-      </c>
-      <c r="H33" t="s">
-        <v>102</v>
-      </c>
-      <c r="I33" t="s">
-        <v>103</v>
-      </c>
-      <c r="J33" t="s">
-        <v>104</v>
-      </c>
       <c r="K33" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L33" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="M33" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N33" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O33" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F34" t="s">
+        <v>116</v>
+      </c>
+      <c r="G34" t="s">
+        <v>117</v>
+      </c>
+      <c r="H34" t="s">
+        <v>97</v>
+      </c>
+      <c r="I34" t="s">
+        <v>118</v>
+      </c>
+      <c r="J34" t="s">
+        <v>101</v>
+      </c>
+      <c r="K34" t="s">
+        <v>119</v>
+      </c>
+      <c r="L34" t="s">
         <v>120</v>
       </c>
-      <c r="G34" t="s">
-        <v>121</v>
-      </c>
-      <c r="H34" t="s">
-        <v>101</v>
-      </c>
-      <c r="I34" t="s">
-        <v>122</v>
-      </c>
-      <c r="J34" t="s">
-        <v>105</v>
-      </c>
-      <c r="K34" t="s">
-        <v>123</v>
-      </c>
-      <c r="L34" t="s">
-        <v>124</v>
-      </c>
       <c r="M34" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="N34" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O34" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F35" t="s">
+        <v>117</v>
+      </c>
+      <c r="G35" t="s">
+        <v>111</v>
+      </c>
+      <c r="H35" t="s">
+        <v>112</v>
+      </c>
+      <c r="I35" t="s">
+        <v>97</v>
+      </c>
+      <c r="J35" t="s">
         <v>121</v>
       </c>
-      <c r="G35" t="s">
-        <v>115</v>
-      </c>
-      <c r="H35" t="s">
-        <v>116</v>
-      </c>
-      <c r="I35" t="s">
-        <v>101</v>
-      </c>
-      <c r="J35" t="s">
-        <v>125</v>
-      </c>
       <c r="K35" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="L35" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="M35" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="N35" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O35" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F36" t="s">
+        <v>208</v>
+      </c>
+      <c r="G36" t="s">
+        <v>117</v>
+      </c>
+      <c r="H36" t="s">
+        <v>97</v>
+      </c>
+      <c r="I36" t="s">
+        <v>112</v>
+      </c>
+      <c r="J36" t="s">
+        <v>98</v>
+      </c>
+      <c r="K36" t="s">
+        <v>102</v>
+      </c>
+      <c r="L36" t="s">
         <v>100</v>
       </c>
-      <c r="G36" t="s">
-        <v>121</v>
-      </c>
-      <c r="H36" t="s">
-        <v>101</v>
-      </c>
-      <c r="I36" t="s">
-        <v>116</v>
-      </c>
-      <c r="J36" t="s">
-        <v>102</v>
-      </c>
-      <c r="K36" t="s">
-        <v>106</v>
-      </c>
-      <c r="L36" t="s">
-        <v>104</v>
-      </c>
       <c r="M36" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="N36" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>10</v>
@@ -2801,2393 +2811,2253 @@
         <v>7</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F37" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G37" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H37" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I37" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="J37" t="s">
+        <v>118</v>
+      </c>
+      <c r="K37" t="s">
+        <v>104</v>
+      </c>
+      <c r="L37" t="s">
+        <v>113</v>
+      </c>
+      <c r="M37" t="s">
+        <v>102</v>
+      </c>
+      <c r="N37" t="s">
         <v>122</v>
       </c>
-      <c r="K37" t="s">
-        <v>108</v>
-      </c>
-      <c r="L37" t="s">
-        <v>117</v>
-      </c>
-      <c r="M37" t="s">
-        <v>106</v>
-      </c>
-      <c r="N37" t="s">
-        <v>126</v>
-      </c>
       <c r="O37" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F38" t="s">
+        <v>112</v>
+      </c>
+      <c r="G38" t="s">
+        <v>98</v>
+      </c>
+      <c r="H38" t="s">
         <v>116</v>
       </c>
-      <c r="G38" t="s">
+      <c r="I38" t="s">
         <v>102</v>
       </c>
-      <c r="H38" t="s">
-        <v>120</v>
-      </c>
-      <c r="I38" t="s">
-        <v>106</v>
-      </c>
       <c r="J38" t="s">
-        <v>100</v>
+        <v>208</v>
       </c>
       <c r="K38" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L38" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="M38" t="s">
+        <v>99</v>
+      </c>
+      <c r="N38" t="s">
         <v>103</v>
       </c>
-      <c r="N38" t="s">
-        <v>107</v>
-      </c>
       <c r="O38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>195</v>
+        <v>3</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="F39" t="s">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="G39" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H39" t="s">
+        <v>120</v>
+      </c>
+      <c r="I39" t="s">
         <v>101</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
+        <v>116</v>
+      </c>
+      <c r="K39" t="s">
+        <v>124</v>
+      </c>
+      <c r="L39" t="s">
+        <v>105</v>
+      </c>
+      <c r="M39" t="s">
         <v>102</v>
       </c>
-      <c r="J39" t="s">
-        <v>103</v>
-      </c>
-      <c r="K39" t="s">
-        <v>130</v>
-      </c>
-      <c r="L39" t="s">
-        <v>109</v>
-      </c>
-      <c r="M39" t="s">
-        <v>106</v>
-      </c>
       <c r="N39" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="O39" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>3</v>
+        <v>155</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F40" t="s">
+        <v>116</v>
+      </c>
+      <c r="G40" t="s">
+        <v>122</v>
+      </c>
+      <c r="H40" t="s">
+        <v>119</v>
+      </c>
+      <c r="I40" t="s">
+        <v>118</v>
+      </c>
+      <c r="J40" t="s">
+        <v>102</v>
+      </c>
+      <c r="K40" t="s">
+        <v>105</v>
+      </c>
+      <c r="L40" t="s">
         <v>100</v>
       </c>
-      <c r="G40" t="s">
-        <v>107</v>
-      </c>
-      <c r="H40" t="s">
-        <v>124</v>
-      </c>
-      <c r="I40" t="s">
-        <v>105</v>
-      </c>
-      <c r="J40" t="s">
-        <v>120</v>
-      </c>
-      <c r="K40" t="s">
-        <v>128</v>
-      </c>
-      <c r="L40" t="s">
-        <v>109</v>
-      </c>
       <c r="M40" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="N40" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="O40" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="F41" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="G41" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="H41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I41" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J41" t="s">
-        <v>106</v>
+        <v>208</v>
       </c>
       <c r="K41" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="L41" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="M41" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="N41" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="O41" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F42" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H42" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="I42" t="s">
+        <v>123</v>
+      </c>
+      <c r="J42" t="s">
+        <v>102</v>
+      </c>
+      <c r="K42" t="s">
+        <v>124</v>
+      </c>
+      <c r="L42" t="s">
         <v>121</v>
       </c>
-      <c r="J42" t="s">
-        <v>100</v>
-      </c>
-      <c r="K42" t="s">
-        <v>120</v>
-      </c>
-      <c r="L42" t="s">
-        <v>125</v>
-      </c>
       <c r="M42" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N42" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="O42" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D43" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="F43" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="G43" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="H43" t="s">
+        <v>112</v>
+      </c>
+      <c r="I43" t="s">
+        <v>116</v>
+      </c>
+      <c r="J43" t="s">
+        <v>121</v>
+      </c>
+      <c r="K43" t="s">
+        <v>114</v>
+      </c>
+      <c r="L43" t="s">
+        <v>98</v>
+      </c>
+      <c r="M43" t="s">
         <v>102</v>
       </c>
-      <c r="I43" t="s">
-        <v>127</v>
-      </c>
-      <c r="J43" t="s">
-        <v>106</v>
-      </c>
-      <c r="K43" t="s">
-        <v>128</v>
-      </c>
-      <c r="L43" t="s">
-        <v>125</v>
-      </c>
-      <c r="M43" t="s">
-        <v>109</v>
-      </c>
       <c r="N43" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O43" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>140</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>52</v>
+        <v>136</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F44" t="s">
+        <v>111</v>
+      </c>
+      <c r="G44" t="s">
+        <v>208</v>
+      </c>
+      <c r="H44" t="s">
+        <v>117</v>
+      </c>
+      <c r="I44" t="s">
+        <v>97</v>
+      </c>
+      <c r="J44" t="s">
+        <v>103</v>
+      </c>
+      <c r="K44" t="s">
+        <v>112</v>
+      </c>
+      <c r="L44" t="s">
+        <v>113</v>
+      </c>
+      <c r="M44" t="s">
         <v>124</v>
       </c>
-      <c r="G44" t="s">
-        <v>107</v>
-      </c>
-      <c r="H44" t="s">
-        <v>116</v>
-      </c>
-      <c r="I44" t="s">
-        <v>120</v>
-      </c>
-      <c r="J44" t="s">
-        <v>125</v>
-      </c>
-      <c r="K44" t="s">
-        <v>118</v>
-      </c>
-      <c r="L44" t="s">
-        <v>102</v>
-      </c>
-      <c r="M44" t="s">
-        <v>106</v>
-      </c>
       <c r="N44" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O44" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>140</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>43</v>
+        <v>136</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>198</v>
+        <v>4</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F45" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G45" t="s">
+        <v>123</v>
+      </c>
+      <c r="H45" t="s">
         <v>100</v>
       </c>
-      <c r="H45" t="s">
-        <v>121</v>
-      </c>
       <c r="I45" t="s">
+        <v>118</v>
+      </c>
+      <c r="J45" t="s">
         <v>101</v>
       </c>
-      <c r="J45" t="s">
-        <v>107</v>
-      </c>
       <c r="K45" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L45" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="M45" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="N45" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="O45" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F46" t="s">
+        <v>208</v>
+      </c>
+      <c r="G46" t="s">
+        <v>122</v>
+      </c>
+      <c r="H46" t="s">
+        <v>116</v>
+      </c>
+      <c r="I46" t="s">
+        <v>101</v>
+      </c>
+      <c r="J46" t="s">
+        <v>123</v>
+      </c>
+      <c r="K46" t="s">
         <v>121</v>
       </c>
-      <c r="G46" t="s">
-        <v>127</v>
-      </c>
-      <c r="H46" t="s">
-        <v>104</v>
-      </c>
-      <c r="I46" t="s">
-        <v>122</v>
-      </c>
-      <c r="J46" t="s">
-        <v>105</v>
-      </c>
-      <c r="K46" t="s">
-        <v>119</v>
-      </c>
       <c r="L46" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="M46" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="N46" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="O46" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F47" t="s">
-        <v>100</v>
+        <v>208</v>
       </c>
       <c r="G47" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="H47" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="I47" t="s">
+        <v>117</v>
+      </c>
+      <c r="J47" t="s">
+        <v>122</v>
+      </c>
+      <c r="K47" t="s">
+        <v>119</v>
+      </c>
+      <c r="L47" t="s">
+        <v>124</v>
+      </c>
+      <c r="M47" t="s">
+        <v>113</v>
+      </c>
+      <c r="N47" t="s">
+        <v>115</v>
+      </c>
+      <c r="O47" t="s">
         <v>105</v>
-      </c>
-      <c r="J47" t="s">
-        <v>127</v>
-      </c>
-      <c r="K47" t="s">
-        <v>125</v>
-      </c>
-      <c r="L47" t="s">
-        <v>102</v>
-      </c>
-      <c r="M47" t="s">
-        <v>128</v>
-      </c>
-      <c r="N47" t="s">
-        <v>106</v>
-      </c>
-      <c r="O47" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>5</v>
+        <v>196</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="F48" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="G48" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H48" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I48" t="s">
         <v>121</v>
       </c>
       <c r="J48" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K48" t="s">
+        <v>102</v>
+      </c>
+      <c r="L48" t="s">
+        <v>115</v>
+      </c>
+      <c r="M48" t="s">
         <v>123</v>
       </c>
-      <c r="L48" t="s">
-        <v>128</v>
-      </c>
-      <c r="M48" t="s">
-        <v>117</v>
-      </c>
       <c r="N48" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="O48" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="F49" t="s">
-        <v>121</v>
+        <v>208</v>
       </c>
       <c r="G49" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H49" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="I49" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J49" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K49" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="L49" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="M49" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="N49" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="O49" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>3</v>
+        <v>145</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>184</v>
       </c>
       <c r="F50" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G50" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H50" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I50" t="s">
-        <v>127</v>
+        <v>208</v>
       </c>
       <c r="J50" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="K50" t="s">
+        <v>123</v>
+      </c>
+      <c r="L50" t="s">
         <v>102</v>
       </c>
-      <c r="L50" t="s">
-        <v>104</v>
-      </c>
       <c r="M50" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="N50" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="O50" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F51" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="G51" t="s">
+        <v>111</v>
+      </c>
+      <c r="H51" t="s">
         <v>116</v>
       </c>
-      <c r="H51" t="s">
-        <v>115</v>
-      </c>
       <c r="I51" t="s">
+        <v>121</v>
+      </c>
+      <c r="J51" t="s">
+        <v>97</v>
+      </c>
+      <c r="K51" t="s">
         <v>100</v>
       </c>
-      <c r="J51" t="s">
-        <v>101</v>
-      </c>
-      <c r="K51" t="s">
-        <v>127</v>
-      </c>
       <c r="L51" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="M51" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="N51" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="O51" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="F52" t="s">
+        <v>111</v>
+      </c>
+      <c r="G52" t="s">
+        <v>117</v>
+      </c>
+      <c r="H52" t="s">
+        <v>116</v>
+      </c>
+      <c r="I52" t="s">
+        <v>118</v>
+      </c>
+      <c r="J52" t="s">
+        <v>97</v>
+      </c>
+      <c r="K52" t="s">
+        <v>103</v>
+      </c>
+      <c r="L52" t="s">
+        <v>102</v>
+      </c>
+      <c r="M52" t="s">
+        <v>99</v>
+      </c>
+      <c r="N52" t="s">
+        <v>100</v>
+      </c>
+      <c r="O52" t="s">
         <v>122</v>
-      </c>
-      <c r="G52" t="s">
-        <v>115</v>
-      </c>
-      <c r="H52" t="s">
-        <v>120</v>
-      </c>
-      <c r="I52" t="s">
-        <v>125</v>
-      </c>
-      <c r="J52" t="s">
-        <v>101</v>
-      </c>
-      <c r="K52" t="s">
-        <v>104</v>
-      </c>
-      <c r="L52" t="s">
-        <v>127</v>
-      </c>
-      <c r="M52" t="s">
-        <v>107</v>
-      </c>
-      <c r="N52" t="s">
-        <v>118</v>
-      </c>
-      <c r="O52" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="F53" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="G53" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H53" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="I53" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="J53" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="K53" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="L53" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="M53" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N53" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="O53" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>152</v>
+        <v>1</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="F54" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G54" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="H54" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="I54" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J54" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="K54" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="L54" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M54" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="N54" t="s">
+        <v>98</v>
+      </c>
+      <c r="O54" t="s">
         <v>119</v>
-      </c>
-      <c r="O54" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>141</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>178</v>
+        <v>137</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G55" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H55" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I55" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="J55" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K55" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="L55" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="M55" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="N55" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="O55" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>179</v>
+        <v>88</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>184</v>
       </c>
       <c r="F56" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="G56" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H56" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="I56" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="J56" t="s">
-        <v>106</v>
+        <v>208</v>
       </c>
       <c r="K56" t="s">
+        <v>120</v>
+      </c>
+      <c r="L56" t="s">
+        <v>124</v>
+      </c>
+      <c r="M56" t="s">
+        <v>115</v>
+      </c>
+      <c r="N56" t="s">
+        <v>128</v>
+      </c>
+      <c r="O56" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>137</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="K57" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="L56" t="s">
-        <v>119</v>
-      </c>
-      <c r="M56" t="s">
-        <v>109</v>
-      </c>
-      <c r="N56" t="s">
-        <v>103</v>
-      </c>
-      <c r="O56" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>141</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="F57" t="s">
-        <v>115</v>
-      </c>
-      <c r="G57" t="s">
-        <v>121</v>
-      </c>
-      <c r="H57" t="s">
-        <v>101</v>
-      </c>
-      <c r="I57" t="s">
-        <v>116</v>
-      </c>
-      <c r="J57" t="s">
+      <c r="L57" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="O57" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="K57" t="s">
-        <v>124</v>
-      </c>
-      <c r="L57" t="s">
-        <v>128</v>
-      </c>
-      <c r="M57" t="s">
-        <v>119</v>
-      </c>
-      <c r="N57" t="s">
-        <v>132</v>
-      </c>
-      <c r="O57" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>141</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>84</v>
+        <v>137</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="F58" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G58" t="s">
+        <v>103</v>
+      </c>
+      <c r="H58" t="s">
+        <v>112</v>
+      </c>
+      <c r="I58" t="s">
+        <v>121</v>
+      </c>
+      <c r="J58" t="s">
         <v>117</v>
       </c>
-      <c r="H58" t="s">
+      <c r="K58" t="s">
+        <v>104</v>
+      </c>
+      <c r="L58" t="s">
+        <v>99</v>
+      </c>
+      <c r="M58" t="s">
+        <v>113</v>
+      </c>
+      <c r="N58" t="s">
+        <v>115</v>
+      </c>
+      <c r="O58" t="s">
         <v>122</v>
-      </c>
-      <c r="I58" t="s">
-        <v>107</v>
-      </c>
-      <c r="J58" t="s">
-        <v>116</v>
-      </c>
-      <c r="K58" t="s">
-        <v>123</v>
-      </c>
-      <c r="L58" t="s">
-        <v>103</v>
-      </c>
-      <c r="M58" t="s">
-        <v>118</v>
-      </c>
-      <c r="N58" t="s">
-        <v>126</v>
-      </c>
-      <c r="O58" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>141</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>85</v>
+        <v>137</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="F59" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="G59" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="H59" t="s">
+        <v>101</v>
+      </c>
+      <c r="I59" t="s">
+        <v>111</v>
+      </c>
+      <c r="J59" t="s">
+        <v>103</v>
+      </c>
+      <c r="K59" t="s">
         <v>124</v>
       </c>
-      <c r="I59" t="s">
-        <v>100</v>
-      </c>
-      <c r="J59" t="s">
-        <v>115</v>
-      </c>
-      <c r="K59" t="s">
-        <v>128</v>
-      </c>
       <c r="L59" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M59" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="N59" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="O59" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>137</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="D60" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="F60" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G60" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H60" t="s">
         <v>121</v>
       </c>
       <c r="I60" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="J60" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="K60" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L60" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="M60" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N60" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O60" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>207</v>
+        <v>6</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>199</v>
+        <v>85</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="F61" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G61" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H61" t="s">
-        <v>116</v>
+        <v>208</v>
       </c>
       <c r="I61" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="J61" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="K61" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="L61" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="M61" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="N61" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O61" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>146</v>
+        <v>4</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F62" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G62" t="s">
+        <v>111</v>
+      </c>
+      <c r="H62" t="s">
+        <v>117</v>
+      </c>
+      <c r="I62" t="s">
         <v>101</v>
       </c>
-      <c r="H62" t="s">
-        <v>105</v>
-      </c>
-      <c r="I62" t="s">
-        <v>115</v>
-      </c>
       <c r="J62" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="K62" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="L62" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="M62" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="N62" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="O62" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="F63" t="s">
+        <v>111</v>
+      </c>
+      <c r="G63" t="s">
+        <v>208</v>
+      </c>
+      <c r="H63" t="s">
+        <v>117</v>
+      </c>
+      <c r="I63" t="s">
+        <v>124</v>
+      </c>
+      <c r="J63" t="s">
         <v>116</v>
       </c>
-      <c r="G63" t="s">
-        <v>120</v>
-      </c>
-      <c r="H63" t="s">
-        <v>125</v>
-      </c>
-      <c r="I63" t="s">
-        <v>101</v>
-      </c>
-      <c r="J63" t="s">
-        <v>108</v>
-      </c>
       <c r="K63" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L63" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="M63" t="s">
         <v>126</v>
       </c>
       <c r="N63" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="O63" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>141</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>88</v>
+        <v>137</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F64" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G64" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="H64" t="s">
+        <v>120</v>
+      </c>
+      <c r="I64" t="s">
+        <v>118</v>
+      </c>
+      <c r="J64" t="s">
+        <v>101</v>
+      </c>
+      <c r="K64" t="s">
+        <v>98</v>
+      </c>
+      <c r="L64" t="s">
         <v>100</v>
       </c>
-      <c r="I64" t="s">
-        <v>101</v>
-      </c>
-      <c r="J64" t="s">
-        <v>116</v>
-      </c>
-      <c r="K64" t="s">
-        <v>102</v>
-      </c>
-      <c r="L64" t="s">
+      <c r="M64" t="s">
         <v>119</v>
       </c>
-      <c r="M64" t="s">
-        <v>109</v>
-      </c>
       <c r="N64" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="O64" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>4</v>
+        <v>160</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="F65" t="s">
+        <v>117</v>
+      </c>
+      <c r="G65" t="s">
+        <v>112</v>
+      </c>
+      <c r="H65" t="s">
         <v>116</v>
       </c>
-      <c r="G65" t="s">
-        <v>115</v>
-      </c>
-      <c r="H65" t="s">
-        <v>121</v>
-      </c>
       <c r="I65" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="J65" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K65" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L65" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="M65" t="s">
         <v>118</v>
       </c>
       <c r="N65" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O65" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F66" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G66" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H66" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I66" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="J66" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="K66" t="s">
-        <v>106</v>
+        <v>208</v>
       </c>
       <c r="L66" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="M66" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="N66" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="O66" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>141</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>160</v>
+        <v>137</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>210</v>
+        <v>181</v>
       </c>
       <c r="F67" t="s">
+        <v>111</v>
+      </c>
+      <c r="G67" t="s">
+        <v>102</v>
+      </c>
+      <c r="H67" t="s">
+        <v>123</v>
+      </c>
+      <c r="I67" t="s">
+        <v>105</v>
+      </c>
+      <c r="J67" t="s">
+        <v>119</v>
+      </c>
+      <c r="K67" t="s">
+        <v>114</v>
+      </c>
+      <c r="L67" t="s">
+        <v>115</v>
+      </c>
+      <c r="M67" t="s">
         <v>121</v>
       </c>
-      <c r="G67" t="s">
-        <v>120</v>
-      </c>
-      <c r="H67" t="s">
-        <v>124</v>
-      </c>
-      <c r="I67" t="s">
+      <c r="N67" t="s">
         <v>122</v>
       </c>
-      <c r="J67" t="s">
-        <v>105</v>
-      </c>
-      <c r="K67" t="s">
-        <v>102</v>
-      </c>
-      <c r="L67" t="s">
-        <v>104</v>
-      </c>
-      <c r="M67" t="s">
-        <v>123</v>
-      </c>
-      <c r="N67" t="s">
-        <v>119</v>
-      </c>
       <c r="O67" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>141</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>77</v>
+        <v>138</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F68" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="G68" t="s">
         <v>116</v>
       </c>
       <c r="H68" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="I68" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="J68" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="K68" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="L68" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="M68" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="N68" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="O68" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F69" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G69" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H69" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I69" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="J69" t="s">
-        <v>106</v>
+        <v>208</v>
       </c>
       <c r="K69" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="L69" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="M69" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="N69" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="O69" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F70" t="s">
-        <v>115</v>
+        <v>208</v>
       </c>
       <c r="G70" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="H70" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="I70" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="J70" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="K70" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="L70" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="M70" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="N70" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="O70" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>142</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>81</v>
+        <v>138</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="F71" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="G71" t="s">
+        <v>208</v>
+      </c>
+      <c r="H71" t="s">
+        <v>100</v>
+      </c>
+      <c r="I71" t="s">
         <v>120</v>
       </c>
-      <c r="H71" t="s">
-        <v>101</v>
-      </c>
-      <c r="I71" t="s">
-        <v>128</v>
-      </c>
       <c r="J71" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="K71" t="s">
+        <v>123</v>
+      </c>
+      <c r="L71" t="s">
         <v>118</v>
       </c>
-      <c r="L71" t="s">
-        <v>117</v>
-      </c>
       <c r="M71" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="N71" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="O71" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>212</v>
+        <v>4</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>213</v>
+        <v>169</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>181</v>
       </c>
       <c r="F72" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G72" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="H72" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="I72" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="J72" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="K72" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="L72" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M72" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="N72" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="O72" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>214</v>
+        <v>155</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F73" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G73" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H73" t="s">
+        <v>97</v>
+      </c>
+      <c r="I73" t="s">
+        <v>113</v>
+      </c>
+      <c r="J73" t="s">
+        <v>119</v>
+      </c>
+      <c r="K73" t="s">
+        <v>99</v>
+      </c>
+      <c r="L73" t="s">
+        <v>124</v>
+      </c>
+      <c r="M73" t="s">
+        <v>98</v>
+      </c>
+      <c r="N73" t="s">
+        <v>115</v>
+      </c>
+      <c r="O73" t="s">
         <v>122</v>
-      </c>
-      <c r="I73" t="s">
-        <v>105</v>
-      </c>
-      <c r="J73" t="s">
-        <v>100</v>
-      </c>
-      <c r="K73" t="s">
-        <v>108</v>
-      </c>
-      <c r="L73" t="s">
-        <v>119</v>
-      </c>
-      <c r="M73" t="s">
-        <v>126</v>
-      </c>
-      <c r="N73" t="s">
-        <v>109</v>
-      </c>
-      <c r="O73" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="E74" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F74" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G74" t="s">
-        <v>121</v>
+        <v>208</v>
       </c>
       <c r="H74" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="I74" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="J74" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="K74" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="L74" t="s">
         <v>118</v>
       </c>
       <c r="M74" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="N74" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="O74" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="F75" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G75" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H75" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="I75" t="s">
+        <v>116</v>
+      </c>
+      <c r="J75" t="s">
+        <v>208</v>
+      </c>
+      <c r="K75" t="s">
+        <v>118</v>
+      </c>
+      <c r="L75" t="s">
+        <v>123</v>
+      </c>
+      <c r="M75" t="s">
+        <v>113</v>
+      </c>
+      <c r="N75" t="s">
         <v>124</v>
       </c>
-      <c r="J75" t="s">
-        <v>102</v>
-      </c>
-      <c r="K75" t="s">
-        <v>127</v>
-      </c>
-      <c r="L75" t="s">
+      <c r="O75" t="s">
         <v>122</v>
-      </c>
-      <c r="M75" t="s">
-        <v>117</v>
-      </c>
-      <c r="N75" t="s">
-        <v>118</v>
-      </c>
-      <c r="O75" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F76" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G76" t="s">
         <v>121</v>
       </c>
       <c r="H76" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I76" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="J76" t="s">
         <v>120</v>
       </c>
       <c r="K76" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L76" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="M76" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="N76" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="O76" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>138</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="D77" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="F77" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="G77" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H77" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="I77" t="s">
+        <v>97</v>
+      </c>
+      <c r="J77" t="s">
+        <v>105</v>
+      </c>
+      <c r="K77" t="s">
+        <v>114</v>
+      </c>
+      <c r="L77" t="s">
+        <v>124</v>
+      </c>
+      <c r="M77" t="s">
         <v>117</v>
       </c>
-      <c r="J77" t="s">
+      <c r="N77" t="s">
         <v>123</v>
       </c>
-      <c r="K77" t="s">
-        <v>103</v>
-      </c>
-      <c r="L77" t="s">
-        <v>128</v>
-      </c>
-      <c r="M77" t="s">
-        <v>102</v>
-      </c>
-      <c r="N77" t="s">
-        <v>119</v>
-      </c>
       <c r="O77" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>154</v>
+        <v>207</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>168</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F78" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="G78" t="s">
+        <v>111</v>
+      </c>
+      <c r="H78" t="s">
+        <v>116</v>
+      </c>
+      <c r="I78" t="s">
+        <v>101</v>
+      </c>
+      <c r="J78" t="s">
+        <v>112</v>
+      </c>
+      <c r="K78" t="s">
         <v>100</v>
       </c>
-      <c r="H78" t="s">
-        <v>124</v>
-      </c>
-      <c r="I78" t="s">
-        <v>105</v>
-      </c>
-      <c r="J78" t="s">
-        <v>107</v>
-      </c>
-      <c r="K78" t="s">
-        <v>118</v>
-      </c>
       <c r="L78" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M78" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N78" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="O78" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>142</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>48</v>
+        <v>138</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="F79" t="s">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="G79" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="H79" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="I79" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="J79" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K79" t="s">
         <v>122</v>
       </c>
       <c r="L79" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="M79" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="N79" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="O79" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>184</v>
       </c>
       <c r="F80" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G80" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="H80" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="I80" t="s">
+        <v>122</v>
+      </c>
+      <c r="J80" t="s">
+        <v>118</v>
+      </c>
+      <c r="K80" t="s">
         <v>102</v>
       </c>
-      <c r="J80" t="s">
+      <c r="L80" t="s">
+        <v>99</v>
+      </c>
+      <c r="M80" t="s">
         <v>124</v>
       </c>
-      <c r="K80" t="s">
-        <v>105</v>
-      </c>
-      <c r="L80" t="s">
-        <v>118</v>
-      </c>
-      <c r="M80" t="s">
-        <v>122</v>
-      </c>
       <c r="N80" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="O80" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>146</v>
+        <v>201</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="F81" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G81" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="H81" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I81" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J81" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="K81" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="L81" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="M81" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="N81" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="O81" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>215</v>
+        <v>2</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F82" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="G82" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H82" t="s">
+        <v>104</v>
+      </c>
+      <c r="I82" t="s">
+        <v>117</v>
+      </c>
+      <c r="J82" t="s">
+        <v>112</v>
+      </c>
+      <c r="K82" t="s">
+        <v>122</v>
+      </c>
+      <c r="L82" t="s">
+        <v>105</v>
+      </c>
+      <c r="M82" t="s">
+        <v>114</v>
+      </c>
+      <c r="N82" t="s">
+        <v>100</v>
+      </c>
+      <c r="O82" t="s">
         <v>120</v>
-      </c>
-      <c r="I82" t="s">
-        <v>105</v>
-      </c>
-      <c r="J82" t="s">
-        <v>116</v>
-      </c>
-      <c r="K82" t="s">
-        <v>104</v>
-      </c>
-      <c r="L82" t="s">
-        <v>124</v>
-      </c>
-      <c r="M82" t="s">
-        <v>127</v>
-      </c>
-      <c r="N82" t="s">
-        <v>102</v>
-      </c>
-      <c r="O82" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>138</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="D83" s="3" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F83" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G83" t="s">
-        <v>127</v>
+        <v>208</v>
       </c>
       <c r="H83" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="I83" t="s">
+        <v>111</v>
+      </c>
+      <c r="J83" t="s">
+        <v>102</v>
+      </c>
+      <c r="K83" t="s">
         <v>118</v>
       </c>
-      <c r="J83" t="s">
-        <v>105</v>
-      </c>
-      <c r="K83" t="s">
-        <v>126</v>
-      </c>
       <c r="L83" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="M83" t="s">
+        <v>122</v>
+      </c>
+      <c r="N83" t="s">
+        <v>112</v>
+      </c>
+      <c r="O83" t="s">
         <v>116</v>
-      </c>
-      <c r="N83" t="s">
-        <v>119</v>
-      </c>
-      <c r="O83" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>3</v>
+        <v>191</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F84" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="G84" t="s">
-        <v>100</v>
+        <v>208</v>
       </c>
       <c r="H84" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="I84" t="s">
+        <v>98</v>
+      </c>
+      <c r="J84" t="s">
+        <v>99</v>
+      </c>
+      <c r="K84" t="s">
         <v>126</v>
       </c>
-      <c r="J84" t="s">
-        <v>122</v>
-      </c>
-      <c r="K84" t="s">
-        <v>106</v>
-      </c>
       <c r="L84" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M84" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="N84" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="O84" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>142</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F85" t="s">
-        <v>105</v>
-      </c>
-      <c r="G85" t="s">
-        <v>125</v>
-      </c>
-      <c r="H85" t="s">
-        <v>121</v>
-      </c>
-      <c r="I85" t="s">
-        <v>103</v>
-      </c>
-      <c r="J85" t="s">
-        <v>118</v>
-      </c>
-      <c r="K85" t="s">
-        <v>119</v>
-      </c>
-      <c r="L85" t="s">
-        <v>126</v>
-      </c>
-      <c r="M85" t="s">
-        <v>108</v>
-      </c>
-      <c r="N85" t="s">
-        <v>117</v>
-      </c>
-      <c r="O85" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>142</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="F86" t="s">
-        <v>115</v>
-      </c>
-      <c r="G86" t="s">
-        <v>120</v>
-      </c>
-      <c r="H86" t="s">
-        <v>108</v>
-      </c>
-      <c r="I86" t="s">
-        <v>121</v>
-      </c>
-      <c r="J86" t="s">
-        <v>116</v>
-      </c>
-      <c r="K86" t="s">
-        <v>126</v>
-      </c>
-      <c r="L86" t="s">
-        <v>109</v>
-      </c>
-      <c r="M86" t="s">
-        <v>118</v>
-      </c>
-      <c r="N86" t="s">
-        <v>104</v>
-      </c>
-      <c r="O86" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>142</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="F87" t="s">
-        <v>102</v>
-      </c>
-      <c r="G87" t="s">
-        <v>100</v>
-      </c>
-      <c r="H87" t="s">
-        <v>121</v>
-      </c>
-      <c r="I87" t="s">
-        <v>115</v>
-      </c>
-      <c r="J87" t="s">
-        <v>106</v>
-      </c>
-      <c r="K87" t="s">
-        <v>122</v>
-      </c>
-      <c r="L87" t="s">
-        <v>101</v>
-      </c>
-      <c r="M87" t="s">
-        <v>126</v>
-      </c>
-      <c r="N87" t="s">
-        <v>116</v>
-      </c>
-      <c r="O87" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="F1:J84" xr:uid="{EA46323A-AC17-4915-8B32-290002EF3BA9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:O18">
     <sortCondition ref="B2:B18"/>
   </sortState>
